--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -444,7 +444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1) Unstandardized coefficients of multilevel analyses for the Study 3 focal mediators and outcomes (No controls)</t>
+          <t>Unstandardised coefficients for Study 3 focal mediators and outcomes — no-controls multilevel path model (N = 438 followers nested in 79 leaders).</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -526,32 +526,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autocratic -&gt; Malicious Env</t>
+          <t>Autocratic -&gt; Malicious envy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Empowering -&gt; Malicious Env</t>
+          <t>Empowering -&gt; Malicious envy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autocratic -&gt; Benign Env</t>
+          <t>Autocratic -&gt; Benign envy</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Empowering -&gt; Benign Env</t>
+          <t>Empowering -&gt; Benign envy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Malicious Env -&gt; Thriving</t>
+          <t>Malicious envy -&gt; Thriving</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Benign Env -&gt; Thriving</t>
+          <t>Benign envy -&gt; Thriving</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ICC Outcome</t>
+          <t>ICC outcome</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Random Slope Var</t>
+          <t>Random slope var</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sample Size</t>
+          <t>Sample size</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -672,26 +672,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.48</v>
+        <v>0.04</v>
       </c>
       <c r="J4" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="K4" t="n">
         <v>0.02</v>
       </c>
       <c r="L4" t="n">
-        <v>4945.8</v>
+        <v>12.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.29</v>
+        <v>0.03</v>
       </c>
       <c r="N4" t="n">
-        <v>0.16</v>
+        <v>0.02</v>
       </c>
       <c r="O4" t="n">
         <v>438</v>
@@ -700,7 +700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>t-value</t>
+          <t>t</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -723,26 +723,28 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.35</v>
+        <v>10.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.14</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4789.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>0.17</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09</v>
+        <v>6.5</v>
       </c>
       <c r="O5" t="n">
         <v>438</v>
@@ -764,8 +766,10 @@
           <t>&lt;.001</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0.015</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -784,29 +788,41 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4868.7</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.12</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
       </c>
       <c r="O6" t="n">
-        <v>79</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7">
@@ -835,29 +851,29 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
       <c r="J7" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>4923.1</v>
+        <v>4831.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="N7" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>79</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8">
@@ -886,107 +902,51 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>4878.3</v>
+        <v>4880.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="O8" t="n">
-        <v>79</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Significant</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Significant</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Significant</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Significant</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Significant</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Significant</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>No controls</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Values</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Values</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Values</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Values</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Values</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Values</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Teams</t>
-        </is>
-      </c>
+          <t>Note. No controls. Sample size = 438 followers across 79 leaders. R² values are pseudo-R² (Snijders &amp; Bosker). 95% CIs via Monte Carlo simulation, B = 20 000.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -444,7 +444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unstandardised coefficients for Study 3 focal mediators and outcomes — no-controls multilevel path model (N = 438 followers nested in 79 leaders).</t>
+          <t>1) Unstandardized coefficients of multilevel analyses for the Study 3 focal mediators and outcomes (no-controls model).</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -526,32 +526,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autocratic -&gt; Malicious envy</t>
+          <t>Autocratic -&gt; Malicious Env</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Empowering -&gt; Malicious envy</t>
+          <t>Empowering -&gt; Malicious Env</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autocratic -&gt; Benign envy</t>
+          <t>Autocratic -&gt; Benign Env</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Empowering -&gt; Benign envy</t>
+          <t>Empowering -&gt; Benign Env</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Malicious envy -&gt; Thriving</t>
+          <t>Malicious Env -&gt; Thriving</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Benign envy -&gt; Thriving</t>
+          <t>Benign Env -&gt; Thriving</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ICC outcome</t>
+          <t>ICC Outcome</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Random slope var</t>
+          <t>Random Slope Var</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sample size</t>
+          <t>Sample Size</t>
         </is>
       </c>
     </row>
@@ -602,22 +602,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.38</v>
+        <v>-0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -634,16 +634,16 @@
         <v>0.03</v>
       </c>
       <c r="L3" t="n">
-        <v>4856.2</v>
+        <v>4821.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="N3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="O3" t="n">
-        <v>438</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.06</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.06</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.05</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -694,32 +694,32 @@
         <v>0.02</v>
       </c>
       <c r="O4" t="n">
-        <v>438</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>t-value</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.43</v>
+        <v>5.25</v>
       </c>
       <c r="C5" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.43</v>
+        <v>-1.88</v>
       </c>
       <c r="E5" t="n">
-        <v>6.83</v>
+        <v>5.43</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.6</v>
+        <v>-5.83</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="N5" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>438</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6">
@@ -768,7 +768,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>438</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="C7" t="n">
         <v>-0.42</v>
@@ -841,13 +841,13 @@
         <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="G7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>-0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>4831.6</v>
+        <v>4795.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>438</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
@@ -883,22 +883,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="G8" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -915,22 +915,22 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>4880.8</v>
+        <v>4847.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="N8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="O8" t="n">
-        <v>438</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Note. No controls. Sample size = 438 followers across 79 leaders. R² values are pseudo-R² (Snijders &amp; Bosker). 95% CIs via Monte Carlo simulation, B = 20 000.</t>
+          <t>Note. N = 360 followers nested within 79 leaders. No controls. 95% CIs derived via Monte Carlo simulation, B = 20 000 replications.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -643,7 +643,7 @@
         <v>0.12</v>
       </c>
       <c r="O3" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4">
@@ -694,7 +694,7 @@
         <v>0.02</v>
       </c>
       <c r="O4" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5">
@@ -747,7 +747,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7">
@@ -873,7 +873,7 @@
         <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8">
@@ -924,13 +924,13 @@
         <v>0.16</v>
       </c>
       <c r="O8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Note. N = 360 followers nested within 79 leaders. No controls. 95% CIs derived via Monte Carlo simulation, B = 20 000 replications.</t>
+          <t>Note. N = 362 followers nested within 79 leaders. No controls. 95% CIs derived via Monte Carlo simulation, B = 20 000 replications.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -444,7 +444,8 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1) Unstandardized coefficients of multilevel analyses for the Study 3 focal mediators and outcomes (no-controls model).</t>
+          <t>1) Unstandardized coefficients of multilevel analyses for the Study 3 focal mediators and outcomes
+因为 controls 拿掉了，系数会变，所以必须重跑。</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -930,23 +931,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Note. N = 362 followers nested within 79 leaders. No controls. 95% CIs derived via Monte Carlo simulation, B = 20 000 replications.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Marginally sig</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Teams</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -644,7 +644,7 @@
         <v>0.12</v>
       </c>
       <c r="O3" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>0.02</v>
       </c>
       <c r="O4" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
@@ -748,7 +748,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
@@ -925,7 +925,7 @@
         <v>0.16</v>
       </c>
       <c r="O8" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -644,7 +644,7 @@
         <v>0.12</v>
       </c>
       <c r="O3" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>0.02</v>
       </c>
       <c r="O4" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5">
@@ -748,7 +748,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8">
@@ -925,7 +925,7 @@
         <v>0.16</v>
       </c>
       <c r="O8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -644,7 +644,7 @@
         <v>0.12</v>
       </c>
       <c r="O3" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>0.02</v>
       </c>
       <c r="O4" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5">
@@ -748,7 +748,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8">
@@ -925,7 +925,7 @@
         <v>0.16</v>
       </c>
       <c r="O8" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -1753,46 +1753,46 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>-0.142</v>
+        <v>-0.151</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.052</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.14</v>
+        <v>-0.148</v>
       </c>
       <c r="E8" s="24" t="n">
         <v>0.052</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.312</v>
+        <v>0.331</v>
       </c>
       <c r="G8" s="24" t="n">
         <v>0.058</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.309</v>
+        <v>0.328</v>
       </c>
       <c r="I8" s="24" t="n">
         <v>0.058</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>-0.082</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K8" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="L8" s="24" t="n">
-        <v>-0.067</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="M8" s="24" t="n">
         <v>0.04</v>
       </c>
       <c r="N8" s="24" t="n">
-        <v>0.075</v>
+        <v>0.109</v>
       </c>
       <c r="O8" s="24" t="n">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" s="32">
@@ -1802,43 +1802,43 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>0.267</v>
+        <v>0.283</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>0.049</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>0.26</v>
+        <v>0.276</v>
       </c>
       <c r="E9" s="24" t="n">
         <v>0.049</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>-0.145</v>
+        <v>-0.154</v>
       </c>
       <c r="G9" s="24" t="n">
         <v>0.052</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.14</v>
+        <v>-0.148</v>
       </c>
       <c r="I9" s="24" t="n">
         <v>0.052</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.118</v>
+        <v>0.125</v>
       </c>
       <c r="K9" s="24" t="n">
         <v>0.043</v>
       </c>
       <c r="L9" s="24" t="n">
-        <v>0.094</v>
+        <v>0.1</v>
       </c>
       <c r="M9" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="N9" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.075</v>
       </c>
       <c r="O9" s="24" t="n">
         <v>0.04</v>
@@ -1912,19 +1912,19 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.234</v>
+        <v>0.248</v>
       </c>
       <c r="K11" s="24" t="n">
         <v>0.046</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="M11" s="24" t="n">
         <v>0.048</v>
       </c>
       <c r="N11" s="24" t="n">
-        <v>-0.112</v>
+        <v>-0.119</v>
       </c>
       <c r="O11" s="24" t="n">
         <v>0.044</v>
@@ -1977,19 +1977,19 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.198</v>
+        <v>-0.21</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.051</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>-0.156</v>
+        <v>-0.165</v>
       </c>
       <c r="M12" s="24" t="n">
         <v>0.053</v>
       </c>
       <c r="N12" s="24" t="n">
-        <v>0.278</v>
+        <v>0.295</v>
       </c>
       <c r="O12" s="24" t="n">
         <v>0.055</v>
@@ -2023,46 +2023,46 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.118</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.118</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.082</v>
+        <v>0.214</v>
       </c>
       <c r="G14" s="24" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="K14" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="H14" s="24" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="I14" s="24" t="n">
+      <c r="L14" s="24" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="M14" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="J14" s="24" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="L14" s="24" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="M14" s="24" t="n">
-        <v>0.044</v>
-      </c>
       <c r="N14" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.118</v>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="32">
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = [填写]; Leader N = [填写]. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 362; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
         </is>
       </c>
     </row>
@@ -4498,6 +4498,11 @@
           <t>X → BE</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4531,6 +4536,11 @@
           <t>X → ME</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4564,6 +4574,11 @@
           <t>BE → THR</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4597,6 +4612,11 @@
           <t>ME → THR</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4630,6 +4650,11 @@
           <t>BE → OCBS</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4663,6 +4688,11 @@
           <t>ME → OCBS</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4696,6 +4726,11 @@
           <t>BE → CWBS</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4729,6 +4764,11 @@
           <t>ME → CWBS</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4762,6 +4802,11 @@
           <t>X × Narcissism → BE</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4795,6 +4840,11 @@
           <t>X × Narcissism → ME</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4828,6 +4878,11 @@
           <t>X × Power Distance → BE</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4861,6 +4916,11 @@
           <t>X × Power Distance → ME</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4894,6 +4954,11 @@
           <t>Indirect effect: X → BE → THR</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4927,6 +4992,11 @@
           <t>Indirect effect: X → ME → THR</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4960,6 +5030,11 @@
           <t>Indirect effect: X → BE → OCBS</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -4993,6 +5068,11 @@
           <t>Indirect effect: X → ME → OCBS</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -5026,6 +5106,11 @@
           <t>Indirect effect: X → BE → CWBS</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -5059,6 +5144,11 @@
           <t>Indirect effect: X → ME → CWBS</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -5092,6 +5182,11 @@
           <t>Conditional indirect effect via BE (Narcissism)</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -5125,6 +5220,11 @@
           <t>Conditional indirect effect via ME (Narcissism)</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -5158,6 +5258,11 @@
           <t>Conditional indirect effect via BE (Power Distance)</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -5191,6 +5296,11 @@
           <t>Conditional indirect effect via ME (Power Distance)</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>Same direction</t>
@@ -5218,6 +5328,8 @@
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27" ht="148.5" customHeight="1" s="32">
       <c r="A27" s="1" t="inlineStr">
         <is>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 362; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
         </is>
       </c>
     </row>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2155,7 +2155,7 @@
         <v>-0.012</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>0.024</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>0.018</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>-0.019</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.041</v>
+        <v>0.048</v>
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="D19" s="24" t="n">
-        <v>0.078</v>
+        <v>0.046</v>
       </c>
       <c r="E19" s="24" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>-0.111</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>-0.098</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>0.067</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.038</v>
+        <v>0.052</v>
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 362; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
         </is>
       </c>
     </row>
@@ -3964,64 +3964,64 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.078</v>
+        <v>0.046</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.041</v>
+        <v>0.263</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.034</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.153</v>
+        <v>0.126</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.064</v>
+        <v>-0.039</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.301</v>
+        <v>0.535</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-0.186</v>
+        <v>-0.162</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.058</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>-0.22</v>
+        <v>-0.156</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.065</v>
+        <v>0.067</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.001</v>
+        <v>0.02</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>-0.347</v>
+        <v>-0.288</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>-0.093</v>
+        <v>-0.024</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>0.156</v>
+        <v>0.117</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>0.076</v>
+        <v>0.082</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>0.041</v>
+        <v>0.155</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.043</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>0.305</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="32">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 360; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
         </is>
       </c>
     </row>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 360; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 365; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
         </is>
       </c>
     </row>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 365; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 363; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
         </is>
       </c>
     </row>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 363; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
         </is>
       </c>
     </row>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -1682,44 +1682,58 @@
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
-        <v>3.821</v>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>3.821***</t>
+        </is>
       </c>
       <c r="C6" s="24" t="n">
         <v>0.094</v>
       </c>
-      <c r="D6" s="24" t="n">
-        <v>3.821</v>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>3.821***</t>
+        </is>
       </c>
       <c r="E6" s="24" t="n">
         <v>0.094</v>
       </c>
-      <c r="F6" s="24" t="n">
-        <v>3.821</v>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>3.821***</t>
+        </is>
       </c>
       <c r="G6" s="24" t="n">
         <v>0.094</v>
       </c>
-      <c r="H6" s="24" t="n">
-        <v>3.821</v>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>3.821***</t>
+        </is>
       </c>
       <c r="I6" s="24" t="n">
         <v>0.094</v>
       </c>
-      <c r="J6" s="24" t="n">
-        <v>3.821</v>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>3.821***</t>
+        </is>
       </c>
       <c r="K6" s="24" t="n">
         <v>0.094</v>
       </c>
-      <c r="L6" s="24" t="n">
-        <v>3.821</v>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>3.821***</t>
+        </is>
       </c>
       <c r="M6" s="24" t="n">
         <v>0.094</v>
       </c>
-      <c r="N6" s="24" t="n">
-        <v>3.821</v>
+      <c r="N6" s="24" t="inlineStr">
+        <is>
+          <t>3.821***</t>
+        </is>
       </c>
       <c r="O6" s="24" t="n">
         <v>0.094</v>
@@ -1752,44 +1766,58 @@
           <t>Autocratic leadership (T1, follower-rated)</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
-        <v>-0.151</v>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>-0.151**</t>
+        </is>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.052</v>
       </c>
-      <c r="D8" s="24" t="n">
-        <v>-0.148</v>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>-0.148**</t>
+        </is>
       </c>
       <c r="E8" s="24" t="n">
         <v>0.052</v>
       </c>
-      <c r="F8" s="24" t="n">
-        <v>0.331</v>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>0.331***</t>
+        </is>
       </c>
       <c r="G8" s="24" t="n">
         <v>0.058</v>
       </c>
-      <c r="H8" s="24" t="n">
-        <v>0.328</v>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>0.328***</t>
+        </is>
       </c>
       <c r="I8" s="24" t="n">
         <v>0.058</v>
       </c>
-      <c r="J8" s="24" t="n">
-        <v>-0.08699999999999999</v>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>-0.087*</t>
+        </is>
       </c>
       <c r="K8" s="24" t="n">
         <v>0.041</v>
       </c>
-      <c r="L8" s="24" t="n">
-        <v>-0.07099999999999999</v>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>-0.071†</t>
+        </is>
       </c>
       <c r="M8" s="24" t="n">
         <v>0.04</v>
       </c>
-      <c r="N8" s="24" t="n">
-        <v>0.109</v>
+      <c r="N8" s="24" t="inlineStr">
+        <is>
+          <t>0.109*</t>
+        </is>
       </c>
       <c r="O8" s="24" t="n">
         <v>0.044</v>
@@ -1801,44 +1829,58 @@
           <t>Empowering leadership (T1, follower-rated)</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
-        <v>0.283</v>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>0.283***</t>
+        </is>
       </c>
       <c r="C9" s="24" t="n">
         <v>0.049</v>
       </c>
-      <c r="D9" s="24" t="n">
-        <v>0.276</v>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>0.276***</t>
+        </is>
       </c>
       <c r="E9" s="24" t="n">
         <v>0.049</v>
       </c>
-      <c r="F9" s="24" t="n">
-        <v>-0.154</v>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>-0.154**</t>
+        </is>
       </c>
       <c r="G9" s="24" t="n">
         <v>0.052</v>
       </c>
-      <c r="H9" s="24" t="n">
-        <v>-0.148</v>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>-0.148**</t>
+        </is>
       </c>
       <c r="I9" s="24" t="n">
         <v>0.052</v>
       </c>
-      <c r="J9" s="24" t="n">
-        <v>0.125</v>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>0.125**</t>
+        </is>
       </c>
       <c r="K9" s="24" t="n">
         <v>0.043</v>
       </c>
-      <c r="L9" s="24" t="n">
-        <v>0.1</v>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>0.1*</t>
+        </is>
       </c>
       <c r="M9" s="24" t="n">
         <v>0.041</v>
       </c>
-      <c r="N9" s="24" t="n">
-        <v>-0.075</v>
+      <c r="N9" s="24" t="inlineStr">
+        <is>
+          <t>-0.075†</t>
+        </is>
       </c>
       <c r="O9" s="24" t="n">
         <v>0.04</v>
@@ -1911,20 +1953,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="24" t="n">
-        <v>0.248</v>
+      <c r="J11" s="24" t="inlineStr">
+        <is>
+          <t>0.248***</t>
+        </is>
       </c>
       <c r="K11" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="L11" s="24" t="n">
-        <v>0.215</v>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>0.215***</t>
+        </is>
       </c>
       <c r="M11" s="24" t="n">
         <v>0.048</v>
       </c>
-      <c r="N11" s="24" t="n">
-        <v>-0.119</v>
+      <c r="N11" s="24" t="inlineStr">
+        <is>
+          <t>-0.119**</t>
+        </is>
       </c>
       <c r="O11" s="24" t="n">
         <v>0.044</v>
@@ -1976,20 +2024,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="24" t="n">
-        <v>-0.21</v>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>-0.21***</t>
+        </is>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.051</v>
       </c>
-      <c r="L12" s="24" t="n">
-        <v>-0.165</v>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>-0.165**</t>
+        </is>
       </c>
       <c r="M12" s="24" t="n">
         <v>0.053</v>
       </c>
-      <c r="N12" s="24" t="n">
-        <v>0.295</v>
+      <c r="N12" s="24" t="inlineStr">
+        <is>
+          <t>0.295***</t>
+        </is>
       </c>
       <c r="O12" s="24" t="n">
         <v>0.055</v>
@@ -2022,44 +2076,58 @@
           <t>Narcissism (T1)</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
-        <v>-0.118</v>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>-0.118*</t>
+        </is>
       </c>
       <c r="C14" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="D14" s="24" t="n">
-        <v>-0.118</v>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>-0.118*</t>
+        </is>
       </c>
       <c r="E14" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="F14" s="24" t="n">
-        <v>0.214</v>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>0.214***</t>
+        </is>
       </c>
       <c r="G14" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="H14" s="24" t="n">
-        <v>0.214</v>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>0.214***</t>
+        </is>
       </c>
       <c r="I14" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="J14" s="24" t="n">
-        <v>-0.118</v>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>-0.118*</t>
+        </is>
       </c>
       <c r="K14" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="L14" s="24" t="n">
-        <v>-0.118</v>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>-0.118*</t>
+        </is>
       </c>
       <c r="M14" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="N14" s="24" t="n">
-        <v>-0.118</v>
+      <c r="N14" s="24" t="inlineStr">
+        <is>
+          <t>-0.118*</t>
+        </is>
       </c>
       <c r="O14" s="24" t="n">
         <v>0.046</v>
@@ -2083,14 +2151,18 @@
       <c r="E15" s="24" t="n">
         <v>0.039</v>
       </c>
-      <c r="F15" s="24" t="n">
-        <v>0.135</v>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>0.135**</t>
+        </is>
       </c>
       <c r="G15" s="24" t="n">
         <v>0.045</v>
       </c>
-      <c r="H15" s="24" t="n">
-        <v>0.135</v>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>0.135**</t>
+        </is>
       </c>
       <c r="I15" s="24" t="n">
         <v>0.045</v>
@@ -2305,8 +2377,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H19" s="24" t="n">
-        <v>-0.111</v>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>-0.111**</t>
+        </is>
       </c>
       <c r="I19" s="24" t="n">
         <v>0.039</v>
@@ -2358,8 +2432,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="24" t="n">
-        <v>-0.098</v>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>-0.098*</t>
+        </is>
       </c>
       <c r="E20" s="24" t="n">
         <v>0.045</v>
@@ -2470,7 +2546,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
         </is>
       </c>
     </row>
@@ -2634,24 +2710,30 @@
           <t>Mediation</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
-        <v>-0.033</v>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>-0.033*</t>
+        </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
           <t>[-0.063, -0.012]</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>-0.029</v>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>-0.029*</t>
+        </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
           <t>[-0.056, -0.010]</t>
         </is>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>0.016</v>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>0.016*</t>
+        </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
@@ -2815,16 +2897,20 @@
           <t>Low power distance (−1 SD)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
-        <v>-0.053</v>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>-0.053*</t>
+        </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
           <t>[-0.099, -0.007]</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
-        <v>-0.046</v>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>-0.046*</t>
+        </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
@@ -2846,8 +2932,10 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
-        <v>0.04</v>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>0.04*</t>
+        </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
@@ -2890,24 +2978,30 @@
           <t>Mediation</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
-        <v>0.062</v>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>0.062*</t>
+        </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
           <t>[0.034, 0.094]</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
-        <v>0.054</v>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>0.054*</t>
+        </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
           <t>[0.028, 0.084]</t>
         </is>
       </c>
-      <c r="F18" s="17" t="n">
-        <v>-0.03</v>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>-0.03*</t>
+        </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -2934,16 +3028,20 @@
           <t>High narcissism (+1 SD)</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
-        <v>0.066</v>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>0.066*</t>
+        </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
           <t>[0.014, 0.118]</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
-        <v>0.058</v>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>0.058*</t>
+        </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
@@ -2965,16 +3063,20 @@
           <t>Low narcissism (−1 SD)</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
-        <v>0.058</v>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>0.058*</t>
+        </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
           <t>[0.010, 0.106]</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
-        <v>0.05</v>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>0.05*</t>
+        </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
@@ -3058,24 +3160,30 @@
           <t>Low power distance (−1 SD)</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
-        <v>0.08799999999999999</v>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>0.088*</t>
+        </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
           <t>[0.025, 0.151]</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
-        <v>0.077</v>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>0.077*</t>
+        </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
           <t>[0.020, 0.134]</t>
         </is>
       </c>
-      <c r="F24" s="17" t="n">
-        <v>-0.043</v>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>-0.043*</t>
+        </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
@@ -3089,16 +3197,20 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
-        <v>-0.052</v>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>-0.052*</t>
+        </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
           <t>[-0.097, -0.007]</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
-        <v>-0.046</v>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>-0.046*</t>
+        </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
@@ -3146,24 +3258,30 @@
           <t>Indirect effect</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n">
-        <v>-0.062</v>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>-0.062*</t>
+        </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
           <t>[-0.098, -0.034]</t>
         </is>
       </c>
-      <c r="D28" s="19" t="n">
-        <v>-0.049</v>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>-0.049*</t>
+        </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
           <t>[-0.082, -0.024]</t>
         </is>
       </c>
-      <c r="F28" s="19" t="n">
-        <v>0.08699999999999999</v>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>0.087*</t>
+        </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
@@ -3177,24 +3295,30 @@
           <t>High narcissism (+1 SD)</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n">
-        <v>-0.067</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>-0.067*</t>
+        </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
           <t>[-0.119, -0.015]</t>
         </is>
       </c>
-      <c r="D29" s="19" t="n">
-        <v>-0.053</v>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>-0.053*</t>
+        </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
           <t>[-0.099, -0.007]</t>
         </is>
       </c>
-      <c r="F29" s="19" t="n">
-        <v>0.093</v>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>0.093*</t>
+        </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
@@ -3208,24 +3332,30 @@
           <t>Low narcissism (−1 SD)</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n">
-        <v>-0.057</v>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>-0.057*</t>
+        </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
           <t>[-0.105, -0.009]</t>
         </is>
       </c>
-      <c r="D30" s="19" t="n">
-        <v>-0.045</v>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>-0.045*</t>
+        </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
           <t>[-0.087, -0.003]</t>
         </is>
       </c>
-      <c r="F30" s="19" t="n">
-        <v>0.081</v>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>0.081*</t>
+        </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
@@ -3270,8 +3400,10 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
-        <v>-0.04</v>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>-0.04*</t>
+        </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
@@ -3286,8 +3418,10 @@
           <t>[-0.066, 0.004]</t>
         </is>
       </c>
-      <c r="F32" s="19" t="n">
-        <v>0.055</v>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>0.055*</t>
+        </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
@@ -3301,24 +3435,30 @@
           <t>Low power distance (−1 SD)</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
-        <v>-0.08400000000000001</v>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>-0.084*</t>
+        </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
           <t>[-0.145, -0.023]</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
-        <v>-0.067</v>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>-0.067*</t>
+        </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
           <t>[-0.119, -0.015]</t>
         </is>
       </c>
-      <c r="F33" s="19" t="n">
-        <v>0.118</v>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>0.118*</t>
+        </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
@@ -3332,8 +3472,10 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B34" s="19" t="n">
-        <v>0.044</v>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>0.044*</t>
+        </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
@@ -3348,8 +3490,10 @@
           <t>[-0.001, 0.073]</t>
         </is>
       </c>
-      <c r="F34" s="19" t="n">
-        <v>-0.063</v>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>-0.063*</t>
+        </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
@@ -3376,24 +3520,30 @@
           <t>Indirect effect</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
-        <v>0.029</v>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>0.029*</t>
+        </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
           <t>[0.011, 0.052]</t>
         </is>
       </c>
-      <c r="D36" s="21" t="n">
-        <v>0.023</v>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>0.023*</t>
+        </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
           <t>[0.008, 0.044]</t>
         </is>
       </c>
-      <c r="F36" s="21" t="n">
-        <v>-0.04</v>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>-0.04*</t>
+        </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
@@ -3454,8 +3604,10 @@
           <t>[-0.006, 0.058]</t>
         </is>
       </c>
-      <c r="F38" s="21" t="n">
-        <v>-0.044</v>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>-0.044*</t>
+        </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
@@ -3500,8 +3652,10 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
-        <v>0.046</v>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>0.046*</t>
+        </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
@@ -3516,8 +3670,10 @@
           <t>[-0.001, 0.075]</t>
         </is>
       </c>
-      <c r="F40" s="21" t="n">
-        <v>-0.063</v>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>-0.063*</t>
+        </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
@@ -3578,8 +3734,10 @@
           <t>[-0.006, 0.060]</t>
         </is>
       </c>
-      <c r="F42" s="21" t="n">
-        <v>-0.045</v>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>-0.045*</t>
+        </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -3824,8 +3982,10 @@
       <c r="H5" s="5" t="n">
         <v>0.067</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>-0.154</v>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>-0.154*</t>
+        </is>
       </c>
       <c r="J5" s="5" t="n">
         <v>0.062</v>
@@ -3839,8 +3999,10 @@
       <c r="M5" s="5" t="n">
         <v>-0.032</v>
       </c>
-      <c r="N5" s="5" t="n">
-        <v>-0.13</v>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>-0.13*</t>
+        </is>
       </c>
       <c r="O5" s="5" t="n">
         <v>0.064</v>
@@ -3901,8 +4063,10 @@
       <c r="H6" s="5" t="n">
         <v>0.094</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>0.285</v>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>0.285***</t>
+        </is>
       </c>
       <c r="J6" s="5" t="n">
         <v>0.059</v>
@@ -3916,8 +4080,10 @@
       <c r="M6" s="5" t="n">
         <v>0.401</v>
       </c>
-      <c r="N6" s="5" t="n">
-        <v>0.249</v>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>0.249***</t>
+        </is>
       </c>
       <c r="O6" s="5" t="n">
         <v>0.06</v>
@@ -3993,8 +4159,10 @@
       <c r="M7" s="5" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="N7" s="5" t="n">
-        <v>-0.156</v>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>-0.156*</t>
+        </is>
       </c>
       <c r="O7" s="5" t="n">
         <v>0.067</v>
@@ -4040,8 +4208,10 @@
           <t>Power distance</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>-0.098</v>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>-0.098*</t>
+        </is>
       </c>
       <c r="E8" s="5" t="n">
         <v>0.039</v>
@@ -4055,8 +4225,10 @@
       <c r="H8" s="5" t="n">
         <v>-0.022</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>0.169</v>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>0.169**</t>
+        </is>
       </c>
       <c r="J8" s="5" t="n">
         <v>0.059</v>
@@ -4070,8 +4242,10 @@
       <c r="M8" s="5" t="n">
         <v>0.285</v>
       </c>
-      <c r="N8" s="5" t="n">
-        <v>0.365</v>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>0.365***</t>
+        </is>
       </c>
       <c r="O8" s="5" t="n">
         <v>0.062</v>
@@ -4085,8 +4259,10 @@
       <c r="R8" s="5" t="n">
         <v>0.487</v>
       </c>
-      <c r="S8" s="5" t="n">
-        <v>-0.196</v>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>-0.196*</t>
+        </is>
       </c>
       <c r="T8" s="5" t="n">
         <v>0.078</v>
@@ -4132,8 +4308,10 @@
       <c r="H9" s="5" t="n">
         <v>0.108</v>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>0.336</v>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>0.336***</t>
+        </is>
       </c>
       <c r="J9" s="5" t="n">
         <v>0.06900000000000001</v>
@@ -4147,8 +4325,10 @@
       <c r="M9" s="5" t="n">
         <v>0.471</v>
       </c>
-      <c r="N9" s="5" t="n">
-        <v>0.288</v>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>0.288***</t>
+        </is>
       </c>
       <c r="O9" s="5" t="n">
         <v>0.07099999999999999</v>
@@ -4209,8 +4389,10 @@
       <c r="H10" s="5" t="n">
         <v>0.061</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>-0.164</v>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>-0.164**</t>
+        </is>
       </c>
       <c r="J10" s="5" t="n">
         <v>0.06</v>
@@ -4224,8 +4406,10 @@
       <c r="M10" s="5" t="n">
         <v>-0.046</v>
       </c>
-      <c r="N10" s="5" t="n">
-        <v>-0.126</v>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>-0.126*</t>
+        </is>
       </c>
       <c r="O10" s="5" t="n">
         <v>0.063</v>
@@ -4271,8 +4455,10 @@
           <t>Power distance</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>-0.111</v>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>-0.111**</t>
+        </is>
       </c>
       <c r="E11" s="5" t="n">
         <v>0.041</v>
@@ -4286,8 +4472,10 @@
       <c r="H11" s="5" t="n">
         <v>-0.031</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>0.201</v>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>0.201**</t>
+        </is>
       </c>
       <c r="J11" s="5" t="n">
         <v>0.066</v>
@@ -4301,8 +4489,10 @@
       <c r="M11" s="5" t="n">
         <v>0.33</v>
       </c>
-      <c r="N11" s="5" t="n">
-        <v>0.423</v>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>0.423***</t>
+        </is>
       </c>
       <c r="O11" s="5" t="n">
         <v>0.06900000000000001</v>
@@ -4316,8 +4506,10 @@
       <c r="R11" s="5" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="S11" s="5" t="n">
-        <v>-0.222</v>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>-0.222**</t>
+        </is>
       </c>
       <c r="T11" s="5" t="n">
         <v>0.082</v>
@@ -4348,8 +4540,10 @@
           <t>Power distance</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>0.067</v>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>0.067†</t>
+        </is>
       </c>
       <c r="E12" s="5" t="n">
         <v>0.038</v>
@@ -4378,8 +4572,10 @@
       <c r="M12" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="N12" s="5" t="n">
-        <v>-0.212</v>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>-0.212**</t>
+        </is>
       </c>
       <c r="O12" s="5" t="n">
         <v>0.062</v>
@@ -4393,8 +4589,10 @@
       <c r="R12" s="5" t="n">
         <v>-0.09</v>
       </c>
-      <c r="S12" s="5" t="n">
-        <v>0.134</v>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>0.134†</t>
+        </is>
       </c>
       <c r="T12" s="5" t="n">
         <v>0.076</v>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2546,7 +2546,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 362; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
         </is>
       </c>
     </row>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2546,7 +2546,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 362; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 363; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
         </is>
       </c>
     </row>
@@ -2761,27 +2761,27 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.038</v>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>[-0.064, 0.004]</t>
+          <t>[-0.076, 0.000]</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.022</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>[-0.058, 0.006]</t>
+          <t>[-0.052, 0.008]</t>
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>[-0.012, 0.040]</t>
+          <t>[-0.014, 0.036]</t>
         </is>
       </c>
     </row>
@@ -2792,27 +2792,27 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.02</v>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>[-0.073, 0.001]</t>
+          <t>[-0.049, 0.009]</t>
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.038</v>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>[-0.067, 0.003]</t>
+          <t>[-0.076, 0.000]</t>
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>[-0.010, 0.046]</t>
+          <t>[-0.008, 0.052]</t>
         </is>
       </c>
     </row>
@@ -2823,27 +2823,27 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>0.006</v>
+        <v>-0.018</v>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>[-0.018, 0.030]</t>
+          <t>[-0.046, 0.010]</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>[-0.018, 0.030]</t>
+          <t>[-0.011, 0.043]</t>
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.011</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>[-0.028, 0.020]</t>
+          <t>[-0.036, 0.014]</t>
         </is>
       </c>
     </row>
@@ -2867,27 +2867,27 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>[-0.039, 0.013]</t>
+          <t>[-0.036, 0.014]</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.014</v>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>[-0.036, 0.014]</t>
+          <t>[-0.040, 0.012]</t>
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>[-0.018, 0.030]</t>
+          <t>[-0.016, 0.032]</t>
         </is>
       </c>
     </row>
@@ -2899,30 +2899,30 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>-0.053*</t>
+          <t>-0.058*</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>[-0.099, -0.007]</t>
+          <t>[-0.106, -0.010]</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-0.046*</t>
+          <t>-0.041*</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>[-0.088, -0.004]</t>
+          <t>[-0.081, -0.001]</t>
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[-0.008, 0.052]</t>
         </is>
       </c>
     </row>
@@ -2934,28 +2934,28 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>0.04*</t>
+          <t>0.047*</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>[0.001, 0.079]</t>
+          <t>[0.004, 0.090]</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.035</v>
+        <v>0.027</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.002, 0.072]</t>
+          <t>[-0.006, 0.060]</t>
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.014</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>[-0.049, 0.009]</t>
+          <t>[-0.040, 0.012]</t>
         </is>
       </c>
     </row>
@@ -3030,30 +3030,30 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>0.066*</t>
+          <t>0.073*</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>[0.014, 0.118]</t>
+          <t>[0.018, 0.128]</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>0.058*</t>
+          <t>0.054*</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>[0.010, 0.106]</t>
+          <t>[0.008, 0.100]</t>
         </is>
       </c>
       <c r="F20" s="17" t="n">
-        <v>-0.032</v>
+        <v>-0.036</v>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>[-0.067, 0.003]</t>
+          <t>[-0.073, 0.001]</t>
         </is>
       </c>
     </row>
@@ -3065,30 +3065,30 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>0.058*</t>
+          <t>0.051*</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>[0.010, 0.106]</t>
+          <t>[0.006, 0.096]</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>0.05*</t>
+          <t>0.054*</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>[0.006, 0.094]</t>
+          <t>[0.008, 0.100]</t>
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>-0.028</v>
+        <v>-0.024</v>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>[-0.061, 0.005]</t>
+          <t>[-0.055, 0.007]</t>
         </is>
       </c>
     </row>
@@ -3099,27 +3099,27 @@
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>0.008</v>
+        <v>0.022</v>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>[-0.016, 0.032]</t>
+          <t>[-0.008, 0.052]</t>
         </is>
       </c>
       <c r="D22" s="17" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>[-0.016, 0.032]</t>
+          <t>[-0.024, 0.024]</t>
         </is>
       </c>
       <c r="F22" s="17" t="n">
-        <v>-0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>[-0.028, 0.020]</t>
+          <t>[-0.037, 0.013]</t>
         </is>
       </c>
     </row>
@@ -3129,28 +3129,30 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
-        <v>0.036</v>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>0.04*</t>
+        </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>[-0.001, 0.073]</t>
+          <t>[0.001, 0.079]</t>
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>[-0.004, 0.066]</t>
+          <t>[-0.007, 0.055]</t>
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>-0.017</v>
+        <v>-0.013</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>[-0.045, 0.011]</t>
+          <t>[-0.039, 0.013]</t>
         </is>
       </c>
     </row>
@@ -3162,32 +3164,32 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>0.088*</t>
+          <t>0.085*</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>[0.025, 0.151]</t>
+          <t>[0.024, 0.146]</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>0.077*</t>
+          <t>0.085*</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>[0.020, 0.134]</t>
+          <t>[0.024, 0.146]</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>-0.043*</t>
+          <t>-0.048*</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>[-0.084, -0.002]</t>
+          <t>[-0.091, -0.005]</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3201,30 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>-0.052*</t>
+          <t>-0.045*</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>[-0.097, -0.007]</t>
+          <t>[-0.087, -0.003]</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>-0.046*</t>
+          <t>-0.061*</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>[-0.088, -0.004]</t>
+          <t>[-0.110, -0.012]</t>
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0.026</v>
+        <v>0.035</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[-0.002, 0.072]</t>
         </is>
       </c>
     </row>
@@ -3297,32 +3299,32 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>-0.067*</t>
+          <t>-0.072*</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>[-0.119, -0.015]</t>
+          <t>[-0.127, -0.017]</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>-0.053*</t>
+          <t>-0.044*</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>[-0.099, -0.007]</t>
+          <t>[-0.085, -0.003]</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>0.093*</t>
+          <t>0.098*</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>[0.028, 0.158]</t>
+          <t>[0.030, 0.166]</t>
         </is>
       </c>
     </row>
@@ -3334,32 +3336,32 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>-0.057*</t>
+          <t>-0.053*</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>[-0.105, -0.009]</t>
+          <t>[-0.099, -0.007]</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>-0.045*</t>
+          <t>-0.054*</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>[-0.087, -0.003]</t>
+          <t>[-0.100, -0.008]</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>0.081*</t>
+          <t>0.077*</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>[0.022, 0.140]</t>
+          <t>[0.020, 0.134]</t>
         </is>
       </c>
     </row>
@@ -3370,27 +3372,27 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>-0.01</v>
+        <v>-0.019</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>[-0.035, 0.015]</t>
+          <t>[-0.048, 0.010]</t>
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>-0.008</v>
+        <v>0.01</v>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>[-0.032, 0.016]</t>
+          <t>[-0.015, 0.035]</t>
         </is>
       </c>
       <c r="F31" s="19" t="n">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>[-0.013, 0.037]</t>
+          <t>[-0.009, 0.051]</t>
         </is>
       </c>
     </row>
@@ -3400,32 +3402,30 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>-0.04*</t>
-        </is>
+      <c r="B32" s="19" t="n">
+        <v>-0.038</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>[-0.079, -0.001]</t>
+          <t>[-0.076, 0.000]</t>
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>-0.031</v>
+        <v>-0.034</v>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>[-0.066, 0.004]</t>
+          <t>[-0.070, 0.002]</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>0.055*</t>
+          <t>0.061*</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>[0.008, 0.102]</t>
+          <t>[0.012, 0.110]</t>
         </is>
       </c>
     </row>
@@ -3437,32 +3437,32 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>-0.084*</t>
+          <t>-0.092*</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>[-0.145, -0.023]</t>
+          <t>[-0.157, -0.027]</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>-0.067*</t>
+          <t>-0.06*</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>[-0.119, -0.015]</t>
+          <t>[-0.109, -0.011]</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>0.118*</t>
+          <t>0.107*</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>[0.041, 0.195]</t>
+          <t>[0.035, 0.179]</t>
         </is>
       </c>
     </row>
@@ -3474,30 +3474,30 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>0.044*</t>
+          <t>0.054*</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>[0.003, 0.085]</t>
+          <t>[0.008, 0.100]</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>[-0.001, 0.073]</t>
+          <t>[-0.006, 0.058]</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>-0.063*</t>
+          <t>-0.046*</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>[-0.113, -0.013]</t>
+          <t>[-0.088, -0.004]</t>
         </is>
       </c>
     </row>
@@ -3558,27 +3558,29 @@
         </is>
       </c>
       <c r="B37" s="21" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>[-0.007, 0.055]</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="n">
         <v>0.026</v>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>[-0.006, 0.058]</t>
         </is>
       </c>
-      <c r="D37" s="21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>[-0.009, 0.049]</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="n">
-        <v>-0.036</v>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>-0.04*</t>
+        </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
-          <t>[-0.073, 0.001]</t>
+          <t>[-0.079, -0.001]</t>
         </is>
       </c>
     </row>
@@ -3589,29 +3591,29 @@
         </is>
       </c>
       <c r="B38" s="21" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>[-0.003, 0.067]</t>
+          <t>[-0.002, 0.070]</t>
         </is>
       </c>
       <c r="D38" s="21" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[-0.009, 0.049]</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>-0.044*</t>
+          <t>-0.04*</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>[-0.085, -0.003]</t>
+          <t>[-0.079, -0.001]</t>
         </is>
       </c>
     </row>
@@ -3622,27 +3624,27 @@
         </is>
       </c>
       <c r="B39" s="21" t="n">
-        <v>-0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>[-0.030, 0.018]</t>
+          <t>[-0.035, 0.015]</t>
         </is>
       </c>
       <c r="D39" s="21" t="n">
-        <v>-0.006</v>
+        <v>0.006</v>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>[-0.030, 0.018]</t>
+          <t>[-0.018, 0.030]</t>
         </is>
       </c>
       <c r="F39" s="21" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
-          <t>[-0.016, 0.032]</t>
+          <t>[-0.024, 0.024]</t>
         </is>
       </c>
     </row>
@@ -3654,30 +3656,32 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>0.046*</t>
+          <t>0.04*</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>[0.004, 0.088]</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="n">
-        <v>0.037</v>
+          <t>[0.001, 0.079]</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>0.043*</t>
+        </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>[-0.001, 0.075]</t>
+          <t>[0.002, 0.084]</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>-0.063*</t>
+          <t>-0.057*</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
-          <t>[-0.113, -0.013]</t>
+          <t>[-0.105, -0.009]</t>
         </is>
       </c>
     </row>
@@ -3688,27 +3692,27 @@
         </is>
       </c>
       <c r="B41" s="21" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>[-0.013, 0.037]</t>
+          <t>[-0.009, 0.049]</t>
         </is>
       </c>
       <c r="D41" s="21" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>[-0.015, 0.035]</t>
+          <t>[-0.019, 0.029]</t>
         </is>
       </c>
       <c r="F41" s="21" t="n">
-        <v>-0.018</v>
+        <v>-0.026</v>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
-          <t>[-0.046, 0.010]</t>
+          <t>[-0.058, 0.006]</t>
         </is>
       </c>
     </row>
@@ -3719,29 +3723,27 @@
         </is>
       </c>
       <c r="B42" s="21" t="n">
-        <v>0.034</v>
+        <v>0.02</v>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>[-0.002, 0.070]</t>
+          <t>[-0.009, 0.049]</t>
         </is>
       </c>
       <c r="D42" s="21" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>[-0.006, 0.060]</t>
-        </is>
-      </c>
-      <c r="F42" s="21" t="inlineStr">
-        <is>
-          <t>-0.045*</t>
-        </is>
+          <t>[-0.000, 0.076]</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="n">
+        <v>-0.031</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
-          <t>[-0.087, -0.003]</t>
+          <t>[-0.066, 0.004]</t>
         </is>
       </c>
     </row>
@@ -4227,24 +4229,24 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>0.169**</t>
+          <t>0.196**</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
         <v>0.059</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.053</v>
+        <v>0.08</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.285</v>
+        <v>0.312</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>0.365***</t>
+          <t>0.346***</t>
         </is>
       </c>
       <c r="O8" s="5" t="n">
@@ -4254,27 +4256,27 @@
         <v>0</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>0.243</v>
+        <v>0.224</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>0.487</v>
+        <v>0.468</v>
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>-0.196*</t>
+          <t>-0.15†</t>
         </is>
       </c>
       <c r="T8" s="5" t="n">
         <v>0.078</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>0.012</v>
+        <v>0.055</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>-0.349</v>
+        <v>-0.303</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>-0.043</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="32">
@@ -4474,24 +4476,24 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>0.201**</t>
+          <t>0.243***</t>
         </is>
       </c>
       <c r="J11" s="5" t="n">
         <v>0.066</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.33</v>
+        <v>0.372</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>0.423***</t>
+          <t>0.398***</t>
         </is>
       </c>
       <c r="O11" s="5" t="n">
@@ -4501,27 +4503,27 @@
         <v>0</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>0.288</v>
+        <v>0.263</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.533</v>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>-0.222**</t>
+          <t>-0.155†</t>
         </is>
       </c>
       <c r="T11" s="5" t="n">
         <v>0.082</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>0.007</v>
+        <v>0.06</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>-0.383</v>
+        <v>-0.316</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>-0.061</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="32">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -2546,7 +2546,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 363; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
         </is>
       </c>
     </row>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -1684,59 +1684,59 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>3.758***</t>
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>3.758***</t>
         </is>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>3.758***</t>
         </is>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>3.758***</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>3.758***</t>
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>3.758***</t>
         </is>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>3.758***</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" s="32">
@@ -1776,11 +1776,11 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>-0.148**</t>
+          <t>-0.136*</t>
         </is>
       </c>
       <c r="E8" s="24" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
@@ -1792,11 +1792,11 @@
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>0.328***</t>
+          <t>0.305***</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>0.276***</t>
+          <t>0.256***</t>
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
@@ -1855,11 +1855,11 @@
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.148**</t>
+          <t>-0.136*</t>
         </is>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.123**</t>
         </is>
       </c>
       <c r="C14" s="24" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.123**</t>
         </is>
       </c>
       <c r="E14" s="24" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>0.214***</t>
+          <t>0.223***</t>
         </is>
       </c>
       <c r="G14" s="24" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>0.214***</t>
+          <t>0.223***</t>
         </is>
       </c>
       <c r="I14" s="24" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.123**</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.123**</t>
         </is>
       </c>
       <c r="M14" s="24" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.123**</t>
         </is>
       </c>
       <c r="O14" s="24" t="n">
@@ -2140,20 +2140,20 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>0.039</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="E15" s="24" t="n">
         <v>0.039</v>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>0.135**</t>
+          <t>0.14**</t>
         </is>
       </c>
       <c r="G15" s="24" t="n">
@@ -2161,26 +2161,26 @@
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>0.135**</t>
+          <t>0.14**</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
         <v>0.045</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="K15" s="24" t="n">
         <v>0.039</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="M15" s="24" t="n">
         <v>0.039</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="O15" s="24" t="n">
         <v>0.039</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.008</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="D18" s="24" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H18" s="24" t="n">
-        <v>-0.019</v>
+        <v>-0.015</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
@@ -2362,28 +2362,28 @@
         </is>
       </c>
       <c r="D19" s="24" t="n">
-        <v>0.046</v>
+        <v>0.042</v>
       </c>
       <c r="E19" s="24" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>-0.107**</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="n">
         <v>0.041</v>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>-0.111**</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="n">
-        <v>0.039</v>
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
@@ -2434,11 +2434,11 @@
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>-0.098*</t>
+          <t>-0.094*</t>
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="H20" s="24" t="n">
-        <v>0.067</v>
+        <v>0.063</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
@@ -2494,25 +2494,25 @@
         </is>
       </c>
       <c r="B21" s="24" t="n">
-        <v>0.142</v>
+        <v>0.131</v>
       </c>
       <c r="D21" s="24" t="n">
-        <v>0.168</v>
+        <v>0.155</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>0.176</v>
+        <v>0.162</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>0.198</v>
+        <v>0.182</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.342</v>
+        <v>0.315</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>0.281</v>
+        <v>0.259</v>
       </c>
       <c r="N21" s="24" t="n">
-        <v>0.253</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1" s="32">
@@ -2522,25 +2522,25 @@
         </is>
       </c>
       <c r="B22" s="31" t="n">
-        <v>0.083</v>
+        <v>0.076</v>
       </c>
       <c r="D22" s="31" t="n">
-        <v>0.096</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F22" s="31" t="n">
-        <v>0.105</v>
+        <v>0.097</v>
       </c>
       <c r="H22" s="31" t="n">
-        <v>0.118</v>
+        <v>0.109</v>
       </c>
       <c r="J22" s="31" t="n">
-        <v>0.218</v>
+        <v>0.201</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>0.184</v>
+        <v>0.169</v>
       </c>
       <c r="N22" s="31" t="n">
-        <v>0.162</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="32">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -5004,7 +5004,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supported</t>
+          <t>Marginal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5029,10 +5029,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Supported</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Marginal</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Direction consistent; not significant in any model.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
@@ -5042,7 +5046,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supported</t>
+          <t>Marginal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5067,10 +5071,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Supported</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Marginal</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Direction consistent; not significant in any model.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -5384,7 +5392,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supported</t>
+          <t>Marginal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5409,10 +5417,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Supported</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Marginal</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Direction consistent; not significant in any model.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
@@ -5422,7 +5434,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supported</t>
+          <t>Marginal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5447,10 +5459,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Supported</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Marginal</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Direction consistent; not significant in any model.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -1684,59 +1684,59 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>3.758***</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.054</v>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>3.758***</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.053</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>3.758***</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.051</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>3.758***</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.051</v>
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>3.758***</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.039</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>3.758***</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.082</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>3.758***</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" s="32">
@@ -1768,31 +1768,31 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>-0.151**</t>
+          <t>-0.494***</t>
         </is>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.052</v>
+        <v>0.064</v>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>-0.136*</t>
+          <t>-0.499***</t>
         </is>
       </c>
       <c r="E8" s="24" t="n">
-        <v>0.054</v>
+        <v>0.064</v>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>0.331***</t>
+          <t>0.577***</t>
         </is>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>0.305***</t>
+          <t>0.597***</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
@@ -1800,27 +1800,27 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>-0.087*</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.041</v>
+        <v>0.051</v>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>-0.071†</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="M8" s="24" t="n">
-        <v>0.04</v>
+        <v>0.079</v>
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>0.109*</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>0.044</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" s="32">
@@ -1831,59 +1831,59 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>0.283***</t>
+          <t>0.524***</t>
         </is>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.049</v>
+        <v>0.059</v>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>0.256***</t>
+          <t>0.521***</t>
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>-0.154**</t>
+          <t>-0.401***</t>
         </is>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.136*</t>
+          <t>-0.396***</t>
         </is>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>0.125**</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.043</v>
+        <v>0.047</v>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>0.1*</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.041</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="N9" s="24" t="inlineStr">
         <is>
-          <t>-0.075†</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="O9" s="24" t="n">
-        <v>0.04</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="32">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>0.248***</t>
+          <t>0.240***</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>0.294***</t>
+        </is>
+      </c>
+      <c r="M11" s="24" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N11" s="24" t="inlineStr">
+        <is>
+          <t>-0.216***</t>
+        </is>
+      </c>
+      <c r="O11" s="24" t="n">
         <v>0.046</v>
-      </c>
-      <c r="L11" s="24" t="inlineStr">
-        <is>
-          <t>0.215***</t>
-        </is>
-      </c>
-      <c r="M11" s="24" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="N11" s="24" t="inlineStr">
-        <is>
-          <t>-0.119**</t>
-        </is>
-      </c>
-      <c r="O11" s="24" t="n">
-        <v>0.044</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" s="32">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>-0.21***</t>
+          <t>-0.177***</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.051</v>
+        <v>0.038</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>-0.165**</t>
+          <t>-0.169**</t>
         </is>
       </c>
       <c r="M12" s="24" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t>0.295***</t>
+          <t>0.181***</t>
         </is>
       </c>
       <c r="O12" s="24" t="n">
-        <v>0.055</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="32">
@@ -2078,59 +2078,59 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>-0.123**</t>
+          <t>-0.051</t>
         </is>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.046</v>
+        <v>0.061</v>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>-0.123**</t>
+          <t>-0.056</t>
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.046</v>
+        <v>0.061</v>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>0.223***</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>0.223***</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.047</v>
+        <v>0.057</v>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.123**</t>
+          <t>-0.038</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>-0.123**</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>-0.123**</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="32">
@@ -2139,51 +2139,61 @@
           <t>Power distance (T1)</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
-        <v>-0.064</v>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>-0.075</t>
+        </is>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>-0.064</v>
+        <v>0.06</v>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>-0.090</t>
+        </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.039</v>
+        <v>0.06</v>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>0.14**</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="G15" s="24" t="n">
-        <v>0.045</v>
+        <v>0.058</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>0.14**</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>-0.064</v>
+        <v>0.057</v>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="L15" s="24" t="n">
-        <v>-0.064</v>
+        <v>0.041</v>
+      </c>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
       </c>
       <c r="M15" s="24" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="N15" s="24" t="n">
-        <v>-0.064</v>
+        <v>0.063</v>
+      </c>
+      <c r="N15" s="24" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
       </c>
       <c r="O15" s="24" t="n">
-        <v>0.039</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" s="32">
@@ -2223,11 +2233,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="24" t="n">
-        <v>-0.008</v>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>-0.038</t>
+        </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.046</v>
+        <v>0.075</v>
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
@@ -2239,11 +2251,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="24" t="n">
-        <v>0.02</v>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>0.061</t>
+        </is>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.048</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
@@ -2292,11 +2306,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D18" s="24" t="n">
-        <v>0.014</v>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>0.039</v>
+        <v>0.075</v>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
@@ -2308,11 +2324,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.015</v>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>0.073</t>
+        </is>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.05</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
@@ -2361,11 +2379,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="24" t="n">
-        <v>0.042</v>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>0.043</v>
+        <v>0.067</v>
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
@@ -2379,11 +2399,11 @@
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>-0.107**</t>
+          <t>-0.138*</t>
         </is>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.041</v>
+        <v>0.063</v>
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
@@ -2434,11 +2454,11 @@
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>-0.094*</t>
+          <t>-0.157*</t>
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>0.047</v>
+        <v>0.063</v>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
@@ -2450,11 +2470,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="24" t="n">
-        <v>0.063</v>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
@@ -2546,7 +2568,7 @@
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 361; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
+          <t>Note. Entries are unstandardized coefficients (b) and standard errors (SE) from multilevel models with followers nested within leaders. Leadership variables were measured at T1, mediators at T2, and outcomes at T3. Thriving at T1 was included only as a baseline control in the model predicting thriving at T3. Interaction terms were estimated only in the mediator interaction models. Pseudo R² values are reported separately for within- and between-leader variance explained. Em dashes indicate that a predictor was not included in a given model. Follower N = 340; Leader N = 79. * p &lt; .05. ** p &lt; .01. *** p &lt; .001.  *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
         </is>
       </c>
     </row>
@@ -2712,32 +2734,32 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>-0.033*</t>
+          <t>-0.118*</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>[-0.063, -0.012]</t>
+          <t>[-0.167, -0.076]</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-0.029*</t>
+          <t>-0.145*</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>[-0.056, -0.010]</t>
+          <t>[-0.213, -0.086]</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>0.016*</t>
+          <t>0.107*</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>[0.005, 0.032]</t>
+          <t>[0.058, 0.163]</t>
         </is>
       </c>
     </row>
@@ -2760,28 +2782,34 @@
           <t>High narcissism (+1 SD)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n">
-        <v>-0.038</v>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>-0.128*</t>
+        </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>[-0.076, 0.000]</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>-0.022</v>
+          <t>[-0.210, -0.046]</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>-0.156*</t>
+        </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>[-0.052, 0.008]</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.011</v>
+          <t>[-0.253, -0.060]</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>0.115*</t>
+        </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>[-0.014, 0.036]</t>
+          <t>[0.039, 0.191]</t>
         </is>
       </c>
     </row>
@@ -2791,28 +2819,34 @@
           <t>Low narcissism (−1 SD)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
-        <v>-0.02</v>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>-0.112*</t>
+        </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>[-0.049, 0.009]</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>-0.038</v>
+          <t>[-0.186, -0.037]</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>-0.137*</t>
+        </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>[-0.076, 0.000]</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.022</v>
+          <t>[-0.224, -0.050]</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>0.101*</t>
+        </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>[-0.008, 0.052]</t>
+          <t>[0.032, 0.170]</t>
         </is>
       </c>
     </row>
@@ -2822,28 +2856,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
-        <v>-0.018</v>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>[-0.046, 0.010]</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0.016</v>
+          <t>[-0.044, 0.011]</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>-0.019</t>
+        </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>[-0.011, 0.043]</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>-0.011</v>
+          <t>[-0.049, 0.010]</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>[-0.036, 0.014]</t>
+          <t>[-0.012, 0.041]</t>
         </is>
       </c>
     </row>
@@ -2866,28 +2906,34 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
-        <v>-0.011</v>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>-0.126*</t>
+        </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>[-0.036, 0.014]</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>-0.014</v>
+          <t>[-0.208, -0.045]</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>-0.155*</t>
+        </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>[-0.040, 0.012]</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>0.008</v>
+          <t>[-0.250, -0.059]</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>0.114*</t>
+        </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>[-0.016, 0.032]</t>
+          <t>[0.039, 0.190]</t>
         </is>
       </c>
     </row>
@@ -2899,30 +2945,32 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>-0.058*</t>
+          <t>-0.114*</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>[-0.106, -0.010]</t>
+          <t>[-0.189, -0.038]</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-0.041*</t>
+          <t>-0.139*</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>[-0.081, -0.001]</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>0.022</v>
+          <t>[-0.226, -0.051]</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>0.102*</t>
+        </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>[-0.008, 0.052]</t>
+          <t>[0.033, 0.172]</t>
         </is>
       </c>
     </row>
@@ -2934,28 +2982,32 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>0.047*</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>[0.004, 0.090]</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>0.027</v>
+          <t>[-0.039, 0.013]</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.006, 0.060]</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>-0.014</v>
+          <t>[-0.043, 0.012]</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>[-0.040, 0.012]</t>
+          <t>[-0.014, 0.037]</t>
         </is>
       </c>
     </row>
@@ -2980,32 +3032,32 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>0.062*</t>
+          <t>0.126*</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>[0.034, 0.094]</t>
+          <t>[0.082, 0.174]</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>0.054*</t>
+          <t>0.154*</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>[0.028, 0.084]</t>
+          <t>[0.094, 0.223]</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>-0.03*</t>
+          <t>-0.113*</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>[-0.056, -0.011]</t>
+          <t>[-0.170, -0.062]</t>
         </is>
       </c>
     </row>
@@ -3030,30 +3082,32 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>0.073*</t>
+          <t>0.132*</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>[0.018, 0.128]</t>
+          <t>[0.048, 0.217]</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>0.054*</t>
+          <t>0.163*</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>[0.008, 0.100]</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>-0.036</v>
+          <t>[0.063, 0.262]</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>-0.119*</t>
+        </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>[-0.073, 0.001]</t>
+          <t>[-0.197, -0.041]</t>
         </is>
       </c>
     </row>
@@ -3065,30 +3119,32 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>0.051*</t>
+          <t>0.118*</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>[0.006, 0.096]</t>
+          <t>[0.040, 0.195]</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>0.054*</t>
+          <t>0.144*</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>[0.008, 0.100]</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>-0.024</v>
+          <t>[0.054, 0.234]</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>-0.106*</t>
+        </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>[-0.055, 0.007]</t>
+          <t>[-0.177, -0.034]</t>
         </is>
       </c>
     </row>
@@ -3098,28 +3154,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
-        <v>0.022</v>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>[-0.008, 0.052]</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>0</v>
+          <t>[-0.012, 0.041]</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>[-0.024, 0.024]</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>-0.012</v>
+          <t>[-0.010, 0.047]</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>-0.013</t>
+        </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>[-0.037, 0.013]</t>
+          <t>[-0.040, 0.013]</t>
         </is>
       </c>
     </row>
@@ -3131,28 +3193,32 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>0.04*</t>
+          <t>0.092*</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>[0.001, 0.079]</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0.024</v>
+          <t>[0.027, 0.156]</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>0.112*</t>
+        </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>[-0.007, 0.055]</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>-0.013</v>
+          <t>[0.038, 0.187]</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>-0.083*</t>
+        </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>[-0.039, 0.013]</t>
+          <t>[-0.143, -0.023]</t>
         </is>
       </c>
     </row>
@@ -3164,32 +3230,32 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>0.085*</t>
+          <t>0.158*</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>[0.024, 0.146]</t>
+          <t>[0.061, 0.256]</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>0.085*</t>
+          <t>0.194*</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>[0.024, 0.146]</t>
+          <t>[0.079, 0.309]</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>-0.048*</t>
+          <t>-0.143*</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>[-0.091, -0.005]</t>
+          <t>[-0.232, -0.053]</t>
         </is>
       </c>
     </row>
@@ -3201,30 +3267,32 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>-0.045*</t>
+          <t>-0.067*</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>[-0.087, -0.003]</t>
+          <t>[-0.119, -0.014]</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>-0.061*</t>
+          <t>-0.082*</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>[-0.110, -0.012]</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>0.035</v>
+          <t>[-0.142, -0.022]</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>0.060*</t>
+        </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>[-0.002, 0.072]</t>
+          <t>[0.011, 0.109]</t>
         </is>
       </c>
     </row>
@@ -3262,32 +3330,32 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>-0.062*</t>
+          <t>-0.102*</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>[-0.098, -0.034]</t>
+          <t>[-0.153, -0.056]</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>-0.049*</t>
+          <t>-0.097*</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>[-0.082, -0.024]</t>
+          <t>[-0.167, -0.033]</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>0.087*</t>
+          <t>0.105*</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>[0.054, 0.124]</t>
+          <t>[0.048, 0.167]</t>
         </is>
       </c>
     </row>
@@ -3299,32 +3367,32 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>-0.072*</t>
+          <t>-0.115*</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>[-0.127, -0.017]</t>
+          <t>[-0.191, -0.039]</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>-0.044*</t>
+          <t>-0.110*</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>[-0.085, -0.003]</t>
+          <t>[-0.184, -0.037]</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>0.098*</t>
+          <t>0.118*</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>[0.030, 0.166]</t>
+          <t>[0.041, 0.195]</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3404,32 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>-0.053*</t>
+          <t>-0.096*</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>[-0.099, -0.007]</t>
+          <t>[-0.163, -0.029]</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>-0.054*</t>
+          <t>-0.092*</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>[-0.100, -0.008]</t>
+          <t>[-0.157, -0.027]</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>0.077*</t>
+          <t>0.099*</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>[0.020, 0.134]</t>
+          <t>[0.031, 0.166]</t>
         </is>
       </c>
     </row>
@@ -3371,28 +3439,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
-        <v>-0.019</v>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>-0.019</t>
+        </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
           <t>[-0.048, 0.010]</t>
         </is>
       </c>
-      <c r="D31" s="19" t="n">
-        <v>0.01</v>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>-0.018</t>
+        </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>[-0.015, 0.035]</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="n">
-        <v>0.021</v>
+          <t>[-0.047, 0.010]</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>0.020</t>
+        </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>[-0.009, 0.051]</t>
+          <t>[-0.010, 0.049]</t>
         </is>
       </c>
     </row>
@@ -3402,30 +3476,34 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
-        <v>-0.038</v>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>-0.084*</t>
+        </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>[-0.076, 0.000]</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>-0.034</v>
+          <t>[-0.145, -0.023]</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>-0.080*</t>
+        </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>[-0.070, 0.002]</t>
+          <t>[-0.139, -0.021]</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>0.061*</t>
+          <t>0.086*</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>[0.012, 0.110]</t>
+          <t>[0.024, 0.148]</t>
         </is>
       </c>
     </row>
@@ -3437,32 +3515,32 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>-0.092*</t>
+          <t>-0.128*</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>[-0.157, -0.027]</t>
+          <t>[-0.210, -0.045]</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>-0.06*</t>
+          <t>-0.122*</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>[-0.109, -0.011]</t>
+          <t>[-0.201, -0.043]</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>0.107*</t>
+          <t>0.131*</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>[0.035, 0.179]</t>
+          <t>[0.047, 0.214]</t>
         </is>
       </c>
     </row>
@@ -3474,30 +3552,32 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>0.054*</t>
+          <t>0.043*</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>[0.008, 0.100]</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>0.026</v>
+          <t>[0.003, 0.084]</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>0.042*</t>
+        </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[0.002, 0.081]</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>-0.046*</t>
+          <t>-0.044*</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>[-0.088, -0.004]</t>
+          <t>[-0.086, -0.003]</t>
         </is>
       </c>
     </row>
@@ -3522,32 +3602,32 @@
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>0.029*</t>
+          <t>0.071*</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>[0.011, 0.052]</t>
+          <t>[0.038, 0.108]</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>0.023*</t>
+          <t>0.068*</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>[0.008, 0.044]</t>
+          <t>[0.023, 0.119]</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>-0.04*</t>
+          <t>-0.073*</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
-          <t>[-0.072, -0.015]</t>
+          <t>[-0.119, -0.032]</t>
         </is>
       </c>
     </row>
@@ -3557,30 +3637,34 @@
           <t>High narcissism (+1 SD)</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
-        <v>0.024</v>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>0.058*</t>
+        </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>[-0.007, 0.055]</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="n">
-        <v>0.026</v>
+          <t>[0.010, 0.107]</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>0.056*</t>
+        </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[0.009, 0.103]</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>-0.04*</t>
+          <t>-0.060*</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
-          <t>[-0.079, -0.001]</t>
+          <t>[-0.109, -0.011]</t>
         </is>
       </c>
     </row>
@@ -3590,30 +3674,34 @@
           <t>Low narcissism (−1 SD)</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
-        <v>0.034</v>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>0.081*</t>
+        </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>[-0.002, 0.070]</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="n">
-        <v>0.02</v>
+          <t>[0.022, 0.141]</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>0.078*</t>
+        </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>[-0.009, 0.049]</t>
+          <t>[0.020, 0.135]</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>-0.04*</t>
+          <t>-0.083*</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>[-0.079, -0.001]</t>
+          <t>[-0.143, -0.023]</t>
         </is>
       </c>
     </row>
@@ -3623,28 +3711,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v>-0.01</v>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>-0.023</t>
+        </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>[-0.035, 0.015]</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="n">
-        <v>0.006</v>
+          <t>[-0.054, 0.008]</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>-0.022</t>
+        </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>[-0.018, 0.030]</t>
-        </is>
-      </c>
-      <c r="F39" s="21" t="n">
-        <v>0</v>
+          <t>[-0.052, 0.009]</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
-          <t>[-0.024, 0.024]</t>
+          <t>[-0.008, 0.054]</t>
         </is>
       </c>
     </row>
@@ -3656,32 +3750,32 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>0.04*</t>
+          <t>0.061*</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>[0.001, 0.079]</t>
+          <t>[0.012, 0.111]</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>0.043*</t>
+          <t>0.058*</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>[0.002, 0.084]</t>
+          <t>[0.010, 0.106]</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>-0.057*</t>
+          <t>-0.063*</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
-          <t>[-0.105, -0.009]</t>
+          <t>[-0.113, -0.012]</t>
         </is>
       </c>
     </row>
@@ -3691,28 +3785,34 @@
           <t>Low power distance (−1 SD)</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v>0.02</v>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>0.079*</t>
+        </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>[-0.009, 0.049]</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="n">
-        <v>0.005</v>
+          <t>[0.021, 0.137]</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>0.075*</t>
+        </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>[-0.019, 0.029]</t>
-        </is>
-      </c>
-      <c r="F41" s="21" t="n">
-        <v>-0.026</v>
+          <t>[0.019, 0.132]</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>-0.081*</t>
+        </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
-          <t>[-0.058, 0.006]</t>
+          <t>[-0.140, -0.022]</t>
         </is>
       </c>
     </row>
@@ -3722,28 +3822,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
-        <v>0.02</v>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>-0.018</t>
+        </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>[-0.009, 0.049]</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="n">
-        <v>0.038</v>
+          <t>[-0.046, 0.010]</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>-0.017</t>
+        </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>[-0.000, 0.076]</t>
-        </is>
-      </c>
-      <c r="F42" s="21" t="n">
-        <v>-0.031</v>
+          <t>[-0.045, 0.011]</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
-          <t>[-0.066, 0.004]</t>
+          <t>[-0.010, 0.046]</t>
         </is>
       </c>
     </row>
@@ -3969,69 +4075,73 @@
           <t>Narcissism</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>-0.012</v>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>-0.038</t>
+        </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.04</v>
+        <v>0.075</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.764</v>
+        <v>0.615</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.091</v>
+        <v>-0.185</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.067</v>
+        <v>0.109</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>-0.154*</t>
+          <t>-0.532***</t>
         </is>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.062</v>
+        <v>0.094</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.276</v>
+        <v>-0.716</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.349</v>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>-0.13*</t>
+          <t>-0.466***</t>
         </is>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.064</v>
+        <v>0.09</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>-0.255</v>
+        <v>-0.643</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.288</v>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>-0.067</t>
+        </is>
       </c>
       <c r="T5" s="5" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>0.764</v>
+        <v>0.607</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>-0.181</v>
+        <v>-0.322</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>0.133</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="32">
@@ -4050,69 +4160,73 @@
           <t>Narcissism</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>0.018</v>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.039</v>
+        <v>0.075</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.645</v>
+        <v>0.643</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.112</v>
       </c>
       <c r="H6" s="5" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>0.552***</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>0.094</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>0.285***</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0.059</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.169</v>
+        <v>0.367</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.401</v>
+        <v>0.736</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>0.249***</t>
+          <t>0.490***</t>
         </is>
       </c>
       <c r="O6" s="5" t="n">
-        <v>0.06</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>0.131</v>
+        <v>0.325</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0.036</v>
+        <v>0.655</v>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>0.062</t>
+        </is>
       </c>
       <c r="T6" s="5" t="n">
-        <v>0.078</v>
+        <v>0.126</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>0.645</v>
+        <v>0.625</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>-0.117</v>
+        <v>-0.186</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>0.189</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="32">
@@ -4131,67 +4245,73 @@
           <t>Power distance</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>0.046</v>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.041</v>
+        <v>0.067</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.263</v>
+        <v>0.654</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.161</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.101</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>-0.526***</t>
+        </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.063</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.535</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-0.162</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.359</v>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>-0.156*</t>
+          <t>-0.472***</t>
         </is>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.067</v>
+        <v>0.089</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>-0.288</v>
+        <v>-0.647</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>0.117</v>
+        <v>-0.298</v>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>-0.053</t>
+        </is>
       </c>
       <c r="T7" s="5" t="n">
-        <v>0.082</v>
+        <v>0.123</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>0.155</v>
+        <v>0.665</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>-0.043</v>
+        <v>-0.294</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>0.277</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="32">
@@ -4212,71 +4332,71 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>-0.098*</t>
+          <t>-0.157*</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.039</v>
+        <v>0.063</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.174</v>
+        <v>-0.28</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.033</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>0.196**</t>
+          <t>0.381***</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.059</v>
+        <v>0.083</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.08</v>
+        <v>0.219</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.312</v>
+        <v>0.544</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>0.346***</t>
+          <t>0.660***</t>
         </is>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.062</v>
+        <v>0.081</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>0.224</v>
+        <v>0.502</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>0.468</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>-0.15†</t>
+          <t>-0.278*</t>
         </is>
       </c>
       <c r="T8" s="5" t="n">
-        <v>0.078</v>
+        <v>0.116</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>0.055</v>
+        <v>0.017</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>-0.303</v>
+        <v>-0.505</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="32">
@@ -4295,69 +4415,73 @@
           <t>Narcissism</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>0.024</v>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>0.061</t>
+        </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.043</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.577</v>
+        <v>0.391</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.078</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.108</v>
+        <v>0.2</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>0.336***</t>
+          <t>0.651***</t>
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.201</v>
+        <v>0.477</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.471</v>
+        <v>0.825</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>0.288***</t>
+          <t>0.543***</t>
         </is>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>0.149</v>
+        <v>0.375</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="S9" s="5" t="n">
-        <v>0.048</v>
+        <v>0.711</v>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>0.108</t>
+        </is>
       </c>
       <c r="T9" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.123</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>0.577</v>
+        <v>0.381</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>-0.121</v>
+        <v>-0.133</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>0.217</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="32">
@@ -4376,69 +4500,73 @@
           <t>Narcissism</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>-0.019</v>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>0.073</t>
+        </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.041</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.643</v>
+        <v>0.305</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.099</v>
+        <v>-0.066</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.061</v>
+        <v>0.212</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>-0.164**</t>
+          <t>-0.331***</t>
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.06</v>
+        <v>0.089</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.282</v>
+        <v>-0.506</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>-0.046</v>
+        <v>-0.157</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>-0.126*</t>
+          <t>-0.461***</t>
         </is>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.063</v>
+        <v>0.08</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.617</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.304</v>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>0.129</t>
+        </is>
       </c>
       <c r="T10" s="5" t="n">
-        <v>0.082</v>
+        <v>0.12</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>0.643</v>
+        <v>0.28</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>-0.199</v>
+        <v>-0.105</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>0.123</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="32">
@@ -4459,71 +4587,71 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>-0.111**</t>
+          <t>-0.138*</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.041</v>
+        <v>0.063</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.007</v>
+        <v>0.03</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.191</v>
+        <v>-0.262</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.014</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>0.243***</t>
+          <t>0.474***</t>
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.066</v>
+        <v>0.08</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.114</v>
+        <v>0.317</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.372</v>
+        <v>0.632</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>0.398***</t>
+          <t>0.720***</t>
         </is>
       </c>
       <c r="O11" s="5" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>0.263</v>
+        <v>0.555</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>0.533</v>
+        <v>0.885</v>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>-0.155†</t>
+          <t>-0.245*</t>
         </is>
       </c>
       <c r="T11" s="5" t="n">
-        <v>0.082</v>
+        <v>0.116</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>0.06</v>
+        <v>0.036</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>-0.316</v>
+        <v>-0.474</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="32">
@@ -4544,69 +4672,71 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>0.067†</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.038</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="5" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>-0.346***</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>0.078</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>-0.078</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0.06</v>
-      </c>
       <c r="K12" s="5" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.196</v>
+        <v>-0.499</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.192</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>-0.212**</t>
+          <t>-0.446***</t>
         </is>
       </c>
       <c r="O12" s="5" t="n">
-        <v>0.062</v>
+        <v>0.076</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>-0.334</v>
+        <v>-0.596</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>-0.09</v>
+        <v>-0.296</v>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>0.134†</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="T12" s="5" t="n">
-        <v>0.076</v>
+        <v>0.109</v>
       </c>
       <c r="U12" s="5" t="n">
-        <v>0.078</v>
+        <v>0.36</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.114</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>0.283</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="32">
@@ -4698,37 +4828,37 @@
           <t>X → BE</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -4736,37 +4866,37 @@
           <t>X → ME</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -4774,37 +4904,37 @@
           <t>BE → THR</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -4812,37 +4942,37 @@
           <t>ME → THR</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -4850,37 +4980,37 @@
           <t>BE → OCBS</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -4888,37 +5018,37 @@
           <t>ME → OCBS</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -4926,37 +5056,37 @@
           <t>BE → CWBS</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
@@ -4964,37 +5094,37 @@
           <t>ME → CWBS</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
@@ -5002,37 +5132,37 @@
           <t>X × Narcissism → BE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Marginal</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>Marginal</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>Direction consistent; not significant in any model.</t>
         </is>
@@ -5044,37 +5174,37 @@
           <t>X × Narcissism → ME</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Marginal</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>Marginal</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>Direction consistent; not significant in any model.</t>
         </is>
@@ -5086,37 +5216,37 @@
           <t>X × Power Distance → BE</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -5124,37 +5254,37 @@
           <t>X × Power Distance → ME</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
@@ -5162,37 +5292,37 @@
           <t>Indirect effect: X → BE → THR</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
@@ -5200,37 +5330,37 @@
           <t>Indirect effect: X → ME → THR</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
@@ -5238,37 +5368,37 @@
           <t>Indirect effect: X → BE → OCBS</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -5276,37 +5406,37 @@
           <t>Indirect effect: X → ME → OCBS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -5314,37 +5444,37 @@
           <t>Indirect effect: X → BE → CWBS</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
@@ -5352,37 +5482,37 @@
           <t>Indirect effect: X → ME → CWBS</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
@@ -5390,37 +5520,37 @@
           <t>Conditional indirect effect via BE (Narcissism)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>Marginal</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>Marginal</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>Direction consistent; not significant in any model.</t>
         </is>
@@ -5432,37 +5562,37 @@
           <t>Conditional indirect effect via ME (Narcissism)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>Marginal</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>Marginal</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>Direction consistent; not significant in any model.</t>
         </is>
@@ -5474,37 +5604,37 @@
           <t>Conditional indirect effect via BE (Power Distance)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
@@ -5512,40 +5642,38 @@
           <t>Conditional indirect effect via ME (Power Distance)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Same direction</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>Same direction</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="H24" s="0" t="inlineStr"/>
+    </row>
     <row r="27" ht="148.5" customHeight="1" s="32">
       <c r="A27" s="1" t="inlineStr">
         <is>

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -1700,19 +1700,19 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
@@ -1728,15 +1728,15 @@
         </is>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.082</v>
+        <v>0.079</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" s="32">
@@ -1784,43 +1784,43 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>0.577***</t>
+          <t>0.593***</t>
         </is>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.061</v>
+        <v>0.058</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>0.597***</t>
+          <t>0.611***</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.108*</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.082</t>
         </is>
       </c>
       <c r="M8" s="24" t="n">
-        <v>0.079</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.023</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>0.068</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" s="32">
@@ -1847,43 +1847,43 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>-0.401***</t>
+          <t>-0.386***</t>
         </is>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.396***</t>
+          <t>-0.385***</t>
         </is>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.051</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.047</v>
+        <v>0.049</v>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>-0.027</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="N9" s="24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="O9" s="24" t="n">
-        <v>0.063</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="32">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>0.240***</t>
+          <t>0.337***</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>0.294***</t>
+          <t>0.329***</t>
         </is>
       </c>
       <c r="M11" s="24" t="n">
-        <v>0.052</v>
+        <v>0.058</v>
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>-0.216***</t>
+          <t>-0.284***</t>
         </is>
       </c>
       <c r="O11" s="24" t="n">
-        <v>0.046</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" s="32">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>-0.177***</t>
+          <t>-0.319***</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.038</v>
+        <v>0.042</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>-0.169**</t>
+          <t>-0.255***</t>
         </is>
       </c>
       <c r="M12" s="24" t="n">
-        <v>0.056</v>
+        <v>0.065</v>
       </c>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t>0.181***</t>
+          <t>0.265***</t>
         </is>
       </c>
       <c r="O12" s="24" t="n">
-        <v>0.049</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="32">
@@ -2094,35 +2094,35 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>0.060</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>-0.036</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.041</v>
+        <v>0.038</v>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="32">
@@ -2157,43 +2157,43 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G15" s="24" t="n">
-        <v>0.058</v>
+        <v>0.055</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.041</v>
+        <v>0.037</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
+          <t>0.019</t>
+        </is>
+      </c>
+      <c r="M15" s="24" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="N15" s="24" t="inlineStr">
+        <is>
           <t>-0.001</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="N15" s="24" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
       <c r="O15" s="24" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" s="32">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
@@ -2326,11 +2326,11 @@
       </c>
       <c r="H18" s="24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
@@ -2399,11 +2399,11 @@
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>-0.138*</t>
+          <t>-0.153*</t>
         </is>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
@@ -2472,11 +2472,11 @@
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
@@ -2734,32 +2734,32 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.166*</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>[-0.167, -0.076]</t>
+          <t>[-0.225, -0.114]</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-0.145*</t>
+          <t>-0.162*</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>[-0.213, -0.086]</t>
+          <t>[-0.238, -0.097]</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>0.107*</t>
+          <t>0.140*</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>[0.058, 0.163]</t>
+          <t>[0.084, 0.206]</t>
         </is>
       </c>
     </row>
@@ -2784,32 +2784,32 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>-0.128*</t>
+          <t>-0.179*</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>[-0.210, -0.046]</t>
+          <t>[-0.287, -0.072]</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-0.156*</t>
+          <t>-0.175*</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>[-0.253, -0.060]</t>
+          <t>[-0.280, -0.070]</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>0.115*</t>
+          <t>0.151*</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>[0.039, 0.191]</t>
+          <t>[0.058, 0.245]</t>
         </is>
       </c>
     </row>
@@ -2821,32 +2821,32 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>-0.112*</t>
+          <t>-0.156*</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>[-0.186, -0.037]</t>
+          <t>[-0.252, -0.060]</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-0.137*</t>
+          <t>-0.153*</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>[-0.224, -0.050]</t>
+          <t>[-0.248, -0.058]</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>0.101*</t>
+          <t>0.133*</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>[0.032, 0.170]</t>
+          <t>[0.048, 0.217]</t>
         </is>
       </c>
     </row>
@@ -2858,32 +2858,32 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.023</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>[-0.044, 0.011]</t>
+          <t>[-0.054, 0.008]</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>[-0.049, 0.010]</t>
+          <t>[-0.052, 0.009]</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>[-0.012, 0.041]</t>
+          <t>[-0.010, 0.048]</t>
         </is>
       </c>
     </row>
@@ -2908,32 +2908,32 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>-0.126*</t>
+          <t>-0.177*</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>[-0.208, -0.045]</t>
+          <t>[-0.283, -0.071]</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-0.155*</t>
+          <t>-0.173*</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>[-0.250, -0.059]</t>
+          <t>[-0.277, -0.068]</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>0.114*</t>
+          <t>0.150*</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>[0.039, 0.190]</t>
+          <t>[0.057, 0.243]</t>
         </is>
       </c>
     </row>
@@ -2945,32 +2945,32 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>-0.114*</t>
+          <t>-0.159*</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>[-0.189, -0.038]</t>
+          <t>[-0.257, -0.062]</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-0.139*</t>
+          <t>-0.155*</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>[-0.226, -0.051]</t>
+          <t>[-0.251, -0.060]</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>0.102*</t>
+          <t>0.134*</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>[0.033, 0.172]</t>
+          <t>[0.049, 0.220]</t>
         </is>
       </c>
     </row>
@@ -2982,32 +2982,32 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>[-0.039, 0.013]</t>
+          <t>[-0.046, 0.010]</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.043, 0.012]</t>
+          <t>[-0.046, 0.011]</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>[-0.014, 0.037]</t>
+          <t>[-0.012, 0.043]</t>
         </is>
       </c>
     </row>
@@ -3032,32 +3032,32 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>0.126*</t>
+          <t>0.176*</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>[0.082, 0.174]</t>
+          <t>[0.124, 0.234]</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>0.154*</t>
+          <t>0.172*</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>[0.094, 0.223]</t>
+          <t>[0.105, 0.249]</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>-0.113*</t>
+          <t>-0.149*</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>[-0.170, -0.062]</t>
+          <t>[-0.215, -0.089]</t>
         </is>
       </c>
     </row>
@@ -3082,32 +3082,32 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>0.132*</t>
+          <t>0.186*</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>[0.048, 0.217]</t>
+          <t>[0.075, 0.296]</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>0.163*</t>
+          <t>0.182*</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>[0.063, 0.262]</t>
+          <t>[0.073, 0.290]</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>-0.119*</t>
+          <t>-0.157*</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>[-0.197, -0.041]</t>
+          <t>[-0.253, -0.060]</t>
         </is>
       </c>
     </row>
@@ -3119,32 +3119,32 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>0.118*</t>
+          <t>0.165*</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>[0.040, 0.195]</t>
+          <t>[0.065, 0.266]</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>0.144*</t>
+          <t>0.161*</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>[0.054, 0.234]</t>
+          <t>[0.063, 0.260]</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>-0.106*</t>
+          <t>-0.139*</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>[-0.177, -0.034]</t>
+          <t>[-0.227, -0.051]</t>
         </is>
       </c>
     </row>
@@ -3156,32 +3156,32 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>[-0.012, 0.041]</t>
+          <t>[-0.009, 0.050]</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>[-0.010, 0.047]</t>
+          <t>[-0.009, 0.050]</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>[-0.040, 0.013]</t>
+          <t>[-0.046, 0.011]</t>
         </is>
       </c>
     </row>
@@ -3193,32 +3193,32 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>0.092*</t>
+          <t>0.128*</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>[0.027, 0.156]</t>
+          <t>[0.046, 0.211]</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>0.112*</t>
+          <t>0.125*</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>[0.038, 0.187]</t>
+          <t>[0.044, 0.207]</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>-0.083*</t>
+          <t>-0.108*</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>[-0.143, -0.023]</t>
+          <t>[-0.181, -0.036]</t>
         </is>
       </c>
     </row>
@@ -3230,32 +3230,32 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>0.158*</t>
+          <t>0.222*</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>[0.061, 0.256]</t>
+          <t>[0.094, 0.350]</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>0.194*</t>
+          <t>0.217*</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>[0.079, 0.309]</t>
+          <t>[0.091, 0.343]</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>-0.143*</t>
+          <t>-0.188*</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>[-0.232, -0.053]</t>
+          <t>[-0.299, -0.076]</t>
         </is>
       </c>
     </row>
@@ -3267,32 +3267,32 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>-0.067*</t>
+          <t>-0.094*</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>[-0.119, -0.014]</t>
+          <t>[-0.159, -0.028]</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>-0.082*</t>
+          <t>-0.092*</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>[-0.142, -0.022]</t>
+          <t>[-0.156, -0.027]</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>0.060*</t>
+          <t>0.079*</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>[0.011, 0.109]</t>
+          <t>[0.021, 0.138]</t>
         </is>
       </c>
     </row>
@@ -3330,32 +3330,32 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>-0.102*</t>
+          <t>-0.189*</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>[-0.153, -0.056]</t>
+          <t>[-0.254, -0.132]</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>-0.097*</t>
+          <t>-0.151*</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>[-0.167, -0.033]</t>
+          <t>[-0.236, -0.073]</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>0.105*</t>
+          <t>0.157*</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>[0.048, 0.167]</t>
+          <t>[0.088, 0.235]</t>
         </is>
       </c>
     </row>
@@ -3367,32 +3367,32 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>-0.115*</t>
+          <t>-0.201*</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>[-0.191, -0.039]</t>
+          <t>[-0.319, -0.083]</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>-0.110*</t>
+          <t>-0.161*</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>[-0.184, -0.037]</t>
+          <t>[-0.259, -0.062]</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>0.118*</t>
+          <t>0.167*</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>[0.041, 0.195]</t>
+          <t>[0.065, 0.268]</t>
         </is>
       </c>
     </row>
@@ -3404,32 +3404,32 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>-0.096*</t>
+          <t>-0.189*</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>[-0.163, -0.029]</t>
+          <t>[-0.302, -0.077]</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>-0.092*</t>
+          <t>-0.151*</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>[-0.157, -0.027]</t>
+          <t>[-0.245, -0.058]</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>0.099*</t>
+          <t>0.157*</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>[0.031, 0.166]</t>
+          <t>[0.061, 0.254]</t>
         </is>
       </c>
     </row>
@@ -3441,32 +3441,32 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>[-0.048, 0.010]</t>
+          <t>[-0.037, 0.014]</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.009</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>[-0.047, 0.010]</t>
+          <t>[-0.033, 0.015]</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>[-0.010, 0.049]</t>
+          <t>[-0.015, 0.034]</t>
         </is>
       </c>
     </row>
@@ -3478,32 +3478,32 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>-0.084*</t>
+          <t>-0.152*</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>[-0.145, -0.023]</t>
+          <t>[-0.246, -0.058]</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>-0.080*</t>
+          <t>-0.121*</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>[-0.139, -0.021]</t>
+          <t>[-0.200, -0.042]</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>0.086*</t>
+          <t>0.126*</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>[0.024, 0.148]</t>
+          <t>[0.045, 0.208]</t>
         </is>
       </c>
     </row>
@@ -3515,32 +3515,32 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>-0.128*</t>
+          <t>-0.239*</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>[-0.210, -0.045]</t>
+          <t>[-0.375, -0.102]</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>-0.122*</t>
+          <t>-0.191*</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>[-0.201, -0.043]</t>
+          <t>[-0.304, -0.078]</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>0.131*</t>
+          <t>0.198*</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>[0.047, 0.214]</t>
+          <t>[0.081, 0.315]</t>
         </is>
       </c>
     </row>
@@ -3552,32 +3552,32 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>0.043*</t>
+          <t>0.087*</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>[0.003, 0.084]</t>
+          <t>[0.025, 0.149]</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>0.042*</t>
+          <t>0.069*</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>[0.002, 0.081]</t>
+          <t>[0.016, 0.123]</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>-0.044*</t>
+          <t>-0.072*</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>[-0.086, -0.003]</t>
+          <t>[-0.126, -0.017]</t>
         </is>
       </c>
     </row>
@@ -3602,32 +3602,32 @@
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>0.071*</t>
+          <t>0.123*</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>[0.038, 0.108]</t>
+          <t>[0.080, 0.172]</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>0.068*</t>
+          <t>0.099*</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>[0.023, 0.119]</t>
+          <t>[0.046, 0.159]</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>-0.073*</t>
+          <t>-0.102*</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
-          <t>[-0.119, -0.032]</t>
+          <t>[-0.158, -0.054]</t>
         </is>
       </c>
     </row>
@@ -3639,32 +3639,32 @@
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>0.058*</t>
+          <t>0.102*</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>[0.010, 0.107]</t>
+          <t>[0.033, 0.172]</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>0.056*</t>
+          <t>0.082*</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>[0.009, 0.103]</t>
+          <t>[0.022, 0.142]</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>-0.060*</t>
+          <t>-0.085*</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
-          <t>[-0.109, -0.011]</t>
+          <t>[-0.146, -0.024]</t>
         </is>
       </c>
     </row>
@@ -3676,32 +3676,32 @@
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>0.081*</t>
+          <t>0.143*</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>[0.022, 0.141]</t>
+          <t>[0.053, 0.233]</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>0.078*</t>
+          <t>0.114*</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>[0.020, 0.135]</t>
+          <t>[0.039, 0.190]</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>-0.083*</t>
+          <t>-0.118*</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>[-0.143, -0.023]</t>
+          <t>[-0.196, -0.041]</t>
         </is>
       </c>
     </row>
@@ -3713,32 +3713,32 @@
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.041*</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>[-0.054, 0.008]</t>
+          <t>[-0.080, -0.001]</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>[-0.052, 0.009]</t>
+          <t>[-0.067, 0.003]</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
-          <t>[-0.008, 0.054]</t>
+          <t>[-0.003, 0.069]</t>
         </is>
       </c>
     </row>
@@ -3750,32 +3750,32 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>0.061*</t>
+          <t>0.119*</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>[0.012, 0.111]</t>
+          <t>[0.041, 0.197]</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>0.058*</t>
+          <t>0.095*</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>[0.010, 0.106]</t>
+          <t>[0.029, 0.161]</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>-0.063*</t>
+          <t>-0.100*</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
-          <t>[-0.113, -0.012]</t>
+          <t>[-0.168, -0.031]</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>0.079*</t>
+          <t>0.126*</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>[0.021, 0.137]</t>
+          <t>[0.045, 0.208]</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>0.075*</t>
+          <t>0.101*</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>[0.019, 0.132]</t>
+          <t>[0.032, 0.170]</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
         <is>
-          <t>-0.081*</t>
+          <t>-0.105*</t>
         </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
-          <t>[-0.140, -0.022]</t>
+          <t>[-0.176, -0.034]</t>
         </is>
       </c>
     </row>
@@ -3824,32 +3824,32 @@
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>[-0.046, 0.010]</t>
+          <t>[-0.030, 0.017]</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>[-0.045, 0.011]</t>
+          <t>[-0.029, 0.018]</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
-          <t>[-0.010, 0.046]</t>
+          <t>[-0.018, 0.029]</t>
         </is>
       </c>
     </row>
@@ -4417,71 +4417,71 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.391</v>
+        <v>0.765</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.078</v>
+        <v>-0.113</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.2</v>
+        <v>0.154</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>0.651***</t>
+          <t>0.629***</t>
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.477</v>
+        <v>0.462</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.825</v>
+        <v>0.797</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>0.543***</t>
+          <t>0.593***</t>
         </is>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>0.375</v>
+        <v>0.432</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>0.711</v>
+        <v>0.755</v>
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="T9" s="5" t="n">
-        <v>0.123</v>
+        <v>0.118</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>0.381</v>
+        <v>0.76</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>-0.133</v>
+        <v>-0.196</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>0.349</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="32">
@@ -4502,71 +4502,71 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.305</v>
+        <v>0.294</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.066</v>
+        <v>-0.062</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.212</v>
+        <v>0.206</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>-0.331***</t>
+          <t>-0.321***</t>
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.506</v>
+        <v>-0.489</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>-0.157</v>
+        <v>-0.153</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>-0.461***</t>
+          <t>-0.449***</t>
         </is>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="P10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>-0.617</v>
+        <v>-0.599</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>-0.304</v>
+        <v>-0.298</v>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="T10" s="5" t="n">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>0.28</v>
+        <v>0.269</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>-0.105</v>
+        <v>-0.098</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>0.364</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="32">
@@ -4587,71 +4587,71 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>-0.138*</t>
+          <t>-0.153*</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.262</v>
+        <v>-0.272</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.034</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>0.474***</t>
+          <t>0.475***</t>
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.317</v>
+        <v>0.324</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.632</v>
+        <v>0.627</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>0.720***</t>
+          <t>0.747***</t>
         </is>
       </c>
       <c r="O11" s="5" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>0.555</v>
+        <v>0.588</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>0.885</v>
+        <v>0.906</v>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>-0.245*</t>
+          <t>-0.272*</t>
         </is>
       </c>
       <c r="T11" s="5" t="n">
-        <v>0.116</v>
+        <v>0.112</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>0.036</v>
+        <v>0.016</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>-0.474</v>
+        <v>-0.491</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="32">
@@ -4672,71 +4672,71 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.345</v>
+        <v>0.837</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.101</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.173</v>
+        <v>0.124</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>-0.346***</t>
+          <t>-0.374***</t>
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.499</v>
+        <v>-0.522</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>-0.192</v>
+        <v>-0.227</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>-0.446***</t>
+          <t>-0.395***</t>
         </is>
       </c>
       <c r="O12" s="5" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>-0.596</v>
+        <v>-0.54</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>-0.296</v>
+        <v>-0.251</v>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="T12" s="5" t="n">
-        <v>0.109</v>
+        <v>0.105</v>
       </c>
       <c r="U12" s="5" t="n">
-        <v>0.36</v>
+        <v>0.842</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>-0.114</v>
+        <v>-0.185</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>0.315</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="32">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -1720,23 +1720,23 @@
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" s="32">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>0.108*</t>
+          <t>0.095†</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>-0.082</t>
+          <t>-0.101</t>
         </is>
       </c>
       <c r="M8" s="24" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
@@ -1863,27 +1863,27 @@
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>-0.051</t>
+          <t>-0.041</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="N9" s="24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="O9" s="24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="32">
@@ -1955,23 +1955,23 @@
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>0.337***</t>
+          <t>0.322***</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>0.329***</t>
+          <t>0.307***</t>
         </is>
       </c>
       <c r="M11" s="24" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>-0.284***</t>
+          <t>-0.262***</t>
         </is>
       </c>
       <c r="O11" s="24" t="n">
@@ -2026,15 +2026,15 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>-0.319***</t>
+          <t>-0.314***</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>-0.255***</t>
+          <t>-0.246***</t>
         </is>
       </c>
       <c r="M12" s="24" t="n">
@@ -2042,11 +2042,11 @@
       </c>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t>0.265***</t>
+          <t>0.256***</t>
         </is>
       </c>
       <c r="O12" s="24" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="32">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
+          <t>-0.041</t>
+        </is>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
           <t>-0.036</t>
         </is>
       </c>
-      <c r="K14" s="24" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>-0.027</t>
-        </is>
-      </c>
       <c r="M14" s="24" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.049</t>
         </is>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="32">
@@ -2173,15 +2173,15 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="M15" s="24" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="O15" s="24" t="n">

--- a/results/Model2.xlsx
+++ b/results/Model2.xlsx
@@ -1800,27 +1800,27 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>0.095†</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.055</v>
+        <v>0.065</v>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>-0.101</t>
+          <t>-0.095</t>
         </is>
       </c>
       <c r="M8" s="24" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>0.077</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" s="32">
@@ -1863,27 +1863,27 @@
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>-0.041</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.048</v>
+        <v>0.057</v>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>-0.015</t>
         </is>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.078</v>
+        <v>0.089</v>
       </c>
       <c r="N9" s="24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="O9" s="24" t="n">
-        <v>0.068</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="32">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>0.322***</t>
+          <t>0.117**</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.037</v>
+        <v>0.043</v>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>0.307***</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="M11" s="24" t="n">
-        <v>0.057</v>
+        <v>0.064</v>
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>-0.262***</t>
+          <t>-0.282***</t>
         </is>
       </c>
       <c r="O11" s="24" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" s="32">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>-0.314***</t>
+          <t>-0.164**</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.043</v>
+        <v>0.052</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>-0.246***</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="M12" s="24" t="n">
-        <v>0.065</v>
+        <v>0.075</v>
       </c>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t>0.256***</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="O12" s="24" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="32">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.041</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.037</v>
+        <v>0.046</v>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>-0.036</t>
+          <t>-0.043</t>
         </is>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.062</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="32">
@@ -2173,27 +2173,27 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.038</v>
+        <v>0.045</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.038</t>
         </is>
       </c>
       <c r="M15" s="24" t="n">
-        <v>0.061</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="O15" s="24" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" s="32">
@@ -2734,32 +2734,32 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>-0.166*</t>
+          <t>-0.053*</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>[-0.225, -0.114]</t>
+          <t>[-0.104, -0.007]</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-0.162*</t>
+          <t>-0.029</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>[-0.238, -0.097]</t>
+          <t>[-0.097, 0.037]</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>0.140*</t>
+          <t>0.146*</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>[0.084, 0.206]</t>
+          <t>[0.086, 0.215]</t>
         </is>
       </c>
     </row>
@@ -2784,32 +2784,32 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>-0.179*</t>
+          <t>-0.057*</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>[-0.287, -0.072]</t>
+          <t>[-0.105, -0.010]</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-0.175*</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>[-0.280, -0.070]</t>
+          <t>[-0.066, 0.004]</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>0.151*</t>
+          <t>0.157*</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>[0.058, 0.245]</t>
+          <t>[0.061, 0.254]</t>
         </is>
       </c>
     </row>
@@ -2821,32 +2821,32 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>-0.156*</t>
+          <t>-0.050*</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>[-0.252, -0.060]</t>
+          <t>[-0.094, -0.006]</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-0.153*</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>[-0.248, -0.058]</t>
+          <t>[-0.060, 0.006]</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>0.133*</t>
+          <t>0.138*</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>[0.048, 0.217]</t>
+          <t>[0.051, 0.225]</t>
         </is>
       </c>
     </row>
@@ -2858,22 +2858,22 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>[-0.054, 0.008]</t>
+          <t>[-0.031, 0.016]</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>[-0.052, 0.009]</t>
+          <t>[-0.027, 0.020]</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>[-0.010, 0.048]</t>
+          <t>[-0.010, 0.049]</t>
         </is>
       </c>
     </row>
@@ -2908,32 +2908,32 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>-0.177*</t>
+          <t>-0.057*</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>[-0.283, -0.071]</t>
+          <t>[-0.104, -0.009]</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-0.173*</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>[-0.277, -0.068]</t>
+          <t>[-0.066, 0.004]</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>0.150*</t>
+          <t>0.156*</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>[0.057, 0.243]</t>
+          <t>[0.060, 0.251]</t>
         </is>
       </c>
     </row>
@@ -2945,32 +2945,32 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>-0.159*</t>
+          <t>-0.051*</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>[-0.257, -0.062]</t>
+          <t>[-0.096, -0.006]</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-0.155*</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>[-0.251, -0.060]</t>
+          <t>[-0.061, 0.005]</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>0.134*</t>
+          <t>0.140*</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>[0.049, 0.220]</t>
+          <t>[0.052, 0.228]</t>
         </is>
       </c>
     </row>
@@ -2982,32 +2982,32 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>[-0.046, 0.010]</t>
+          <t>[-0.029, 0.018]</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.046, 0.011]</t>
+          <t>[-0.027, 0.020]</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>[-0.012, 0.043]</t>
+          <t>[-0.011, 0.043]</t>
         </is>
       </c>
     </row>
@@ -3032,32 +3032,32 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>0.176*</t>
+          <t>0.056*</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>[0.124, 0.234]</t>
+          <t>[0.007, 0.109]</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>0.172*</t>
+          <t>0.031</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>[0.105, 0.249]</t>
+          <t>[-0.038, 0.102]</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>-0.149*</t>
+          <t>-0.154*</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>[-0.215, -0.089]</t>
+          <t>[-0.224, -0.092]</t>
         </is>
       </c>
     </row>
@@ -3082,32 +3082,32 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>0.186*</t>
+          <t>0.059*</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>[0.075, 0.296]</t>
+          <t>[0.011, 0.108]</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>0.182*</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>[0.073, 0.290]</t>
+          <t>[-0.003, 0.068]</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>-0.157*</t>
+          <t>-0.163*</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>[-0.253, -0.060]</t>
+          <t>[-0.262, -0.063]</t>
         </is>
       </c>
     </row>
@@ -3119,32 +3119,32 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>0.165*</t>
+          <t>0.053*</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>[0.065, 0.266]</t>
+          <t>[0.007, 0.098]</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>0.161*</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>[0.063, 0.260]</t>
+          <t>[-0.005, 0.063]</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>-0.139*</t>
+          <t>-0.145*</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>[-0.227, -0.051]</t>
+          <t>[-0.235, -0.054]</t>
         </is>
       </c>
     </row>
@@ -3156,22 +3156,22 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>[-0.009, 0.050]</t>
+          <t>[-0.017, 0.030]</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>[-0.009, 0.050]</t>
+          <t>[-0.020, 0.027]</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>[-0.046, 0.011]</t>
+          <t>[-0.047, 0.010]</t>
         </is>
       </c>
     </row>
@@ -3193,32 +3193,32 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>0.128*</t>
+          <t>0.041*</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>[0.046, 0.211]</t>
+          <t>[0.001, 0.081]</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>0.125*</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>[0.044, 0.207]</t>
+          <t>[-0.008, 0.053]</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>-0.108*</t>
+          <t>-0.113*</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>[-0.181, -0.036]</t>
+          <t>[-0.187, -0.038]</t>
         </is>
       </c>
     </row>
@@ -3230,32 +3230,32 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>0.222*</t>
+          <t>0.071*</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>[0.094, 0.350]</t>
+          <t>[0.017, 0.125]</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>0.217*</t>
+          <t>0.039*</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>[0.091, 0.343]</t>
+          <t>[0.000, 0.078]</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>-0.188*</t>
+          <t>-0.195*</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>[-0.299, -0.076]</t>
+          <t>[-0.310, -0.080]</t>
         </is>
       </c>
     </row>
@@ -3267,32 +3267,32 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>-0.094*</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>[-0.159, -0.028]</t>
+          <t>[-0.064, 0.004]</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>-0.092*</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>[-0.156, -0.027]</t>
+          <t>[-0.044, 0.011]</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>0.079*</t>
+          <t>0.082*</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>[0.021, 0.138]</t>
+          <t>[0.022, 0.142]</t>
         </is>
       </c>
     </row>
@@ -3330,32 +3330,32 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>-0.189*</t>
+          <t>-0.097*</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>[-0.254, -0.132]</t>
+          <t>[-0.164, -0.035]</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>-0.151*</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>[-0.236, -0.073]</t>
+          <t>[-0.111, 0.065]</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>0.157*</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>[0.088, 0.235]</t>
+          <t>[-0.042, 0.100]</t>
         </is>
       </c>
     </row>
@@ -3367,32 +3367,32 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>-0.201*</t>
+          <t>-0.103*</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>[-0.319, -0.083]</t>
+          <t>[-0.173, -0.033]</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>-0.161*</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>[-0.259, -0.062]</t>
+          <t>[-0.055, 0.007]</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>0.167*</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>[0.065, 0.268]</t>
+          <t>[-0.005, 0.064]</t>
         </is>
       </c>
     </row>
@@ -3404,32 +3404,32 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>-0.189*</t>
+          <t>-0.097*</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>[-0.302, -0.077]</t>
+          <t>[-0.164, -0.030]</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>-0.151*</t>
+          <t>-0.023</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>[-0.245, -0.058]</t>
+          <t>[-0.053, 0.008]</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>0.157*</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>[0.061, 0.254]</t>
+          <t>[-0.005, 0.061]</t>
         </is>
       </c>
     </row>
@@ -3441,32 +3441,32 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>[-0.037, 0.014]</t>
+          <t>[-0.029, 0.018]</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>[-0.033, 0.015]</t>
+          <t>[-0.025, 0.022]</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>[-0.015, 0.034]</t>
+          <t>[-0.022, 0.025]</t>
         </is>
       </c>
     </row>
@@ -3478,32 +3478,32 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>-0.152*</t>
+          <t>-0.078*</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>[-0.246, -0.058]</t>
+          <t>[-0.135, -0.020]</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>-0.121*</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>[-0.200, -0.042]</t>
+          <t>[-0.046, 0.010]</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>0.126*</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>[0.045, 0.208]</t>
+          <t>[-0.008, 0.053]</t>
         </is>
       </c>
     </row>
@@ -3515,32 +3515,32 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>-0.239*</t>
+          <t>-0.122*</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>[-0.375, -0.102]</t>
+          <t>[-0.201, -0.043]</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>-0.191*</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>[-0.304, -0.078]</t>
+          <t>[-0.061, 0.005]</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>0.198*</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>[0.081, 0.315]</t>
+          <t>[-0.002, 0.072]</t>
         </is>
       </c>
     </row>
@@ -3552,32 +3552,32 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>0.087*</t>
+          <t>0.044*</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>[0.025, 0.149]</t>
+          <t>[0.003, 0.086]</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>0.069*</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>[0.016, 0.123]</t>
+          <t>[-0.014, 0.035]</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>-0.072*</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>[-0.126, -0.017]</t>
+          <t>[-0.038, 0.013]</t>
         </is>
       </c>
     </row>
@@ -3602,32 +3602,32 @@
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>0.123*</t>
+          <t>0.063*</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>[0.080, 0.172]</t>
+          <t>[0.023, 0.108]</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>0.099*</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>[0.046, 0.159]</t>
+          <t>[-0.042, 0.073]</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>-0.102*</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
-          <t>[-0.158, -0.054]</t>
+          <t>[-0.065, 0.028]</t>
         </is>
       </c>
     </row>
@@ -3639,32 +3639,32 @@
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>0.102*</t>
+          <t>0.052*</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>[0.033, 0.172]</t>
+          <t>[0.007, 0.097]</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>0.082*</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>[0.022, 0.142]</t>
+          <t>[-0.013, 0.038]</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>-0.085*</t>
+          <t>-0.015</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
-          <t>[-0.146, -0.024]</t>
+          <t>[-0.042, 0.012]</t>
         </is>
       </c>
     </row>
@@ -3676,32 +3676,32 @@
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>0.143*</t>
+          <t>0.073*</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>[0.053, 0.233]</t>
+          <t>[0.018, 0.128]</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>0.114*</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>[0.039, 0.190]</t>
+          <t>[-0.011, 0.045]</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>[-0.196, -0.041]</t>
+          <t>[-0.050, 0.009]</t>
         </is>
       </c>
     </row>
@@ -3713,32 +3713,32 @@
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>-0.041*</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>[-0.080, -0.001]</t>
+          <t>[-0.051, 0.009]</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>[-0.067, 0.003]</t>
+          <t>[-0.028, 0.019]</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
-          <t>[-0.003, 0.069]</t>
+          <t>[-0.018, 0.029]</t>
         </is>
       </c>
     </row>
@@ -3750,32 +3750,32 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>0.119*</t>
+          <t>0.061*</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>[0.041, 0.197]</t>
+          <t>[0.011, 0.110]</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>0.095*</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>[0.029, 0.161]</t>
+          <t>[-0.013, 0.040]</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>-0.100*</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
-          <t>[-0.168, -0.031]</t>
+          <t>[-0.046, 0.011]</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>0.126*</t>
+          <t>0.065*</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>[0.045, 0.208]</t>
+          <t>[0.013, 0.116]</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>0.101*</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>[0.032, 0.170]</t>
+          <t>[-0.012, 0.041]</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
         <is>
-          <t>-0.105*</t>
+          <t>-0.019</t>
         </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
-          <t>[-0.176, -0.034]</t>
+          <t>[-0.047, 0.010]</t>
         </is>
       </c>
     </row>
@@ -3824,32 +3824,32 @@
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>[-0.030, 0.017]</t>
+          <t>[-0.027, 0.020]</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>[-0.029, 0.018]</t>
+          <t>[-0.024, 0.023]</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
-          <t>[-0.018, 0.029]</t>
+          <t>[-0.023, 0.024]</t>
         </is>
       </c>
     </row>
